--- a/data/SEMANA ATUAL/rodada 8/ANTIPULGAS.xlsx
+++ b/data/SEMANA ATUAL/rodada 8/ANTIPULGAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="279">
   <si>
     <t>Sigla Loja</t>
   </si>
@@ -32,6 +32,15 @@
   </si>
   <si>
     <t>20/08/2026 (Qui)</t>
+  </si>
+  <si>
+    <t>21/08/2026 (Sex)</t>
+  </si>
+  <si>
+    <t>22/08/2026 (Sáb)</t>
+  </si>
+  <si>
+    <t>23/08/2026 (Dom)</t>
   </si>
   <si>
     <t>ABNO-RJ</t>
@@ -1207,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F270"/>
+  <dimension ref="A1:I270"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1215,7 +1224,7 @@
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1234,10 +1243,19 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>1162.98</v>
@@ -1251,10 +1269,19 @@
       <c r="F2" s="1">
         <v>1998.09</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="1">
+        <v>1833.12</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1648.73</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2758.11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>4531.860000000001</v>
@@ -1268,33 +1295,51 @@
       <c r="F3" s="1">
         <v>3361.91</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="1">
+        <v>3277.85</v>
+      </c>
+      <c r="H3" s="1">
+        <v>3747.009999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>3413.84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
-        <v>4527.399999999999</v>
+        <v>4527.4</v>
       </c>
       <c r="D4" s="1">
         <v>3435.55</v>
       </c>
       <c r="E4" s="1">
-        <v>4740.179999999999</v>
+        <v>4740.179999999998</v>
       </c>
       <c r="F4" s="1">
         <v>4031.579999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="1">
+        <v>3502.609999999999</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4805.159999999999</v>
+      </c>
+      <c r="I4" s="1">
+        <v>4086.559999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>3681.189999999999</v>
       </c>
       <c r="D5" s="1">
-        <v>3836.629999999999</v>
+        <v>3836.630000000001</v>
       </c>
       <c r="E5" s="1">
         <v>2460.22</v>
@@ -1302,10 +1347,19 @@
       <c r="F5" s="1">
         <v>1842.32</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="1">
+        <v>3178.309999999999</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2759.82</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5443.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>2084.59</v>
@@ -1319,10 +1373,19 @@
       <c r="F6" s="1">
         <v>1116.11</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="1">
+        <v>1774.28</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1467.3</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1820.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1">
         <v>1961.67</v>
@@ -1334,18 +1397,27 @@
         <v>1027.7</v>
       </c>
       <c r="F7" s="1">
-        <v>2983.58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>2983.580000000001</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2873.400000000001</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3809.77</v>
+      </c>
+      <c r="I7" s="1">
+        <v>961.6900000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>629.41</v>
       </c>
       <c r="D8" s="1">
-        <v>909.6700000000001</v>
+        <v>909.67</v>
       </c>
       <c r="E8" s="1">
         <v>1059.89</v>
@@ -1353,13 +1425,22 @@
       <c r="F8" s="1">
         <v>1020.95</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="1">
+        <v>1771.4</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1813.8</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1195.54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1">
-        <v>3102.889999999999</v>
+        <v>3102.89</v>
       </c>
       <c r="D9" s="1">
         <v>1492.28</v>
@@ -1370,10 +1451,19 @@
       <c r="F9" s="1">
         <v>1771.04</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="1">
+        <v>2378.9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>644.72</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2161.81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1">
         <v>1674.97</v>
@@ -1387,10 +1477,19 @@
       <c r="F10" s="1">
         <v>139.97</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="1">
+        <v>751.85</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1128.12</v>
+      </c>
+      <c r="I10" s="1">
+        <v>396.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1">
         <v>1697.4</v>
@@ -1402,15 +1501,24 @@
         <v>2305.46</v>
       </c>
       <c r="F11" s="1">
-        <v>3602.150000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>3602.149999999999</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3012.489999999999</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4198.27</v>
+      </c>
+      <c r="I11" s="1">
+        <v>3743.669999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1">
-        <v>2286.929999999999</v>
+        <v>2286.93</v>
       </c>
       <c r="D12" s="1">
         <v>1793.95</v>
@@ -1421,10 +1529,19 @@
       <c r="F12" s="1">
         <v>1506.9</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="1">
+        <v>1998.99</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1511.85</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2859.170000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1">
         <v>2260.12</v>
@@ -1433,15 +1550,24 @@
         <v>3526.09</v>
       </c>
       <c r="E13" s="1">
-        <v>2914.809999999999</v>
+        <v>2914.81</v>
       </c>
       <c r="F13" s="1">
-        <v>3770.389999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>3770.39</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2588.85</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2984.5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1186.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1">
         <v>3358.25</v>
@@ -1450,32 +1576,50 @@
         <v>1644.03</v>
       </c>
       <c r="E14" s="1">
-        <v>4226.609999999999</v>
+        <v>4226.61</v>
       </c>
       <c r="F14" s="1">
         <v>2051.87</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="1">
+        <v>2868.99</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2705.410000000001</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2509.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
-        <v>6883.430000000001</v>
+        <v>6883.429999999998</v>
       </c>
       <c r="D15" s="1">
-        <v>5760.169999999999</v>
+        <v>5760.169999999998</v>
       </c>
       <c r="E15" s="1">
-        <v>4047.469999999999</v>
+        <v>4047.47</v>
       </c>
       <c r="F15" s="1">
-        <v>4580.08</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>4580.079999999999</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4170.09</v>
+      </c>
+      <c r="H15" s="1">
+        <v>5975.089999999998</v>
+      </c>
+      <c r="I15" s="1">
+        <v>6372.289999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1">
         <v>1190.08</v>
@@ -1489,16 +1633,25 @@
       <c r="F16" s="1">
         <v>346.97</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="1">
+        <v>299.97</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1388.16</v>
+      </c>
+      <c r="I16" s="1">
+        <v>425.46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
         <v>3476.02</v>
       </c>
       <c r="D17" s="1">
-        <v>2858.179999999999</v>
+        <v>2858.18</v>
       </c>
       <c r="E17" s="1">
         <v>1488.5</v>
@@ -1506,10 +1659,19 @@
       <c r="F17" s="1">
         <v>4264.93</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="1">
+        <v>2258.34</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2627.27</v>
+      </c>
+      <c r="I17" s="1">
+        <v>3200.55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1">
         <v>1176.78</v>
@@ -1523,10 +1685,19 @@
       <c r="F18" s="1">
         <v>1830.91</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="1">
+        <v>519.13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1898.62</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2059.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1">
         <v>2492.579999999999</v>
@@ -1540,13 +1711,22 @@
       <c r="F19" s="1">
         <v>1678.55</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="1">
+        <v>1702.35</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2684.88</v>
+      </c>
+      <c r="I19" s="1">
+        <v>620.0700000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1">
-        <v>3521.679999999999</v>
+        <v>3521.68</v>
       </c>
       <c r="D20" s="1">
         <v>2062.15</v>
@@ -1555,18 +1735,27 @@
         <v>1007.18</v>
       </c>
       <c r="F20" s="1">
-        <v>2346.28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>2346.279999999999</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2370.37</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3264.5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>3122.529999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1">
-        <v>680.52</v>
+        <v>680.5200000000001</v>
       </c>
       <c r="D21" s="1">
-        <v>511.34</v>
+        <v>511.3399999999999</v>
       </c>
       <c r="E21" s="1">
         <v>898.28</v>
@@ -1574,10 +1763,19 @@
       <c r="F21" s="1">
         <v>1160.09</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="1">
+        <v>577.5700000000001</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1118.37</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1088.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1">
         <v>959.46</v>
@@ -1591,13 +1789,22 @@
       <c r="F22" s="1">
         <v>1181.87</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="1">
+        <v>584.37</v>
+      </c>
+      <c r="H22" s="1">
+        <v>965.8500000000001</v>
+      </c>
+      <c r="I22" s="1">
+        <v>856.9200000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D23" s="1">
         <v>499.81</v>
@@ -1606,12 +1813,21 @@
         <v>336.98</v>
       </c>
       <c r="F23" s="1">
-        <v>927.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>927.1200000000001</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1057.33</v>
+      </c>
+      <c r="H23" s="1">
+        <v>499.03</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1233.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1">
         <v>1644.98</v>
@@ -1625,13 +1841,22 @@
       <c r="F24" s="1">
         <v>2061.28</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="1">
+        <v>1618.26</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1412.8</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1230.51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1">
-        <v>581.7099999999999</v>
+        <v>581.71</v>
       </c>
       <c r="D25" s="1">
         <v>757.63</v>
@@ -1642,16 +1867,25 @@
       <c r="F25" s="1">
         <v>365.95</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="1">
+        <v>876.1999999999998</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1040.05</v>
+      </c>
+      <c r="I25" s="1">
+        <v>687.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1">
         <v>4452.33</v>
       </c>
       <c r="D26" s="1">
-        <v>5200.82</v>
+        <v>5200.820000000001</v>
       </c>
       <c r="E26" s="1">
         <v>2991.3</v>
@@ -1659,10 +1893,19 @@
       <c r="F26" s="1">
         <v>3070.279999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="1">
+        <v>3131.79</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2369.23</v>
+      </c>
+      <c r="I26" s="1">
+        <v>3446.799999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1">
         <v>2305.11</v>
@@ -1676,16 +1919,25 @@
       <c r="F27" s="1">
         <v>1433.46</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="1">
+        <v>1685.69</v>
+      </c>
+      <c r="H27" s="1">
+        <v>2657.079999999999</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2241.36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1">
-        <v>4510.339999999999</v>
+        <v>4510.34</v>
       </c>
       <c r="D28" s="1">
-        <v>4066.339999999999</v>
+        <v>4066.340000000001</v>
       </c>
       <c r="E28" s="1">
         <v>2299.54</v>
@@ -1693,13 +1945,22 @@
       <c r="F28" s="1">
         <v>2285.37</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="1">
+        <v>3536.649999999999</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1964.25</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2446.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C29" s="1">
-        <v>4991.829999999998</v>
+        <v>4991.83</v>
       </c>
       <c r="D29" s="1">
         <v>3385.98</v>
@@ -1708,12 +1969,21 @@
         <v>3691.100000000001</v>
       </c>
       <c r="F29" s="1">
-        <v>4339.69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>4339.689999999999</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4715.969999999999</v>
+      </c>
+      <c r="H29" s="1">
+        <v>4508.119999999998</v>
+      </c>
+      <c r="I29" s="1">
+        <v>5831.079999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1">
         <v>1938</v>
@@ -1722,15 +1992,24 @@
         <v>1553.96</v>
       </c>
       <c r="E30" s="1">
-        <v>676.8899999999999</v>
+        <v>676.89</v>
       </c>
       <c r="F30" s="1">
         <v>1376.46</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="1">
+        <v>1701.76</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1743.62</v>
+      </c>
+      <c r="I30" s="1">
+        <v>979.45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1">
         <v>1380.8</v>
@@ -1742,12 +2021,21 @@
         <v>980.5599999999999</v>
       </c>
       <c r="F31" s="1">
-        <v>807.6500000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>807.65</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2460.47</v>
+      </c>
+      <c r="H31" s="1">
+        <v>172.98</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1004.76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C32" s="1">
         <v>1512.23</v>
@@ -1759,32 +2047,50 @@
         <v>2395</v>
       </c>
       <c r="F32" s="1">
-        <v>2134.150000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>2134.15</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2835.930000000001</v>
+      </c>
+      <c r="H32" s="1">
+        <v>4372.7</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2236.93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C33" s="1">
         <v>4282.35</v>
       </c>
       <c r="D33" s="1">
-        <v>4599.429999999999</v>
+        <v>4599.43</v>
       </c>
       <c r="E33" s="1">
-        <v>3858.029999999999</v>
+        <v>3858.03</v>
       </c>
       <c r="F33" s="1">
         <v>3716.089999999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33" s="1">
+        <v>4592.999999999999</v>
+      </c>
+      <c r="H33" s="1">
+        <v>3724.869999999999</v>
+      </c>
+      <c r="I33" s="1">
+        <v>4241.909999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C34" s="1">
-        <v>4278.53</v>
+        <v>4278.530000000001</v>
       </c>
       <c r="D34" s="1">
         <v>2671.85</v>
@@ -1795,10 +2101,19 @@
       <c r="F34" s="1">
         <v>2503.69</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="1">
+        <v>3953.390000000001</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3025.759999999999</v>
+      </c>
+      <c r="I34" s="1">
+        <v>6973.59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C35" s="1">
         <v>2125.79</v>
@@ -1812,10 +2127,19 @@
       <c r="F35" s="1">
         <v>788.3099999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="1">
+        <v>677.86</v>
+      </c>
+      <c r="H35" s="1">
+        <v>803.4000000000001</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1421.32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C36" s="1">
         <v>3804.27</v>
@@ -1829,27 +2153,45 @@
       <c r="F36" s="1">
         <v>3932.399999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="1">
+        <v>3028.819999999999</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2073</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2161.11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C37" s="1">
-        <v>6302.81</v>
+        <v>6302.809999999999</v>
       </c>
       <c r="D37" s="1">
-        <v>3598.950000000001</v>
+        <v>3598.95</v>
       </c>
       <c r="E37" s="1">
-        <v>4153.909999999999</v>
+        <v>4153.91</v>
       </c>
       <c r="F37" s="1">
         <v>4356.52</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" s="1">
+        <v>3151.76</v>
+      </c>
+      <c r="H37" s="1">
+        <v>3636.22</v>
+      </c>
+      <c r="I37" s="1">
+        <v>4220.969999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1">
         <v>1536.97</v>
@@ -1863,10 +2205,19 @@
       <c r="F38" s="1">
         <v>1446.65</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="G38" s="1">
+        <v>1144.16</v>
+      </c>
+      <c r="H38" s="1">
+        <v>921.9</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1712.11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C39" s="1">
         <v>661.02</v>
@@ -1880,10 +2231,19 @@
       <c r="F39" s="1">
         <v>1126.89</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="1">
+        <v>283.7</v>
+      </c>
+      <c r="H39" s="1">
+        <v>872.9</v>
+      </c>
+      <c r="I39" s="1">
+        <v>729.4299999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C40" s="1">
         <v>1642.93</v>
@@ -1897,10 +2257,19 @@
       <c r="F40" s="1">
         <v>1321.06</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" s="1">
+        <v>4733.009999999999</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1888.55</v>
+      </c>
+      <c r="I40" s="1">
+        <v>3148.719999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C41" s="1">
         <v>1031.61</v>
@@ -1914,10 +2283,19 @@
       <c r="F41" s="1">
         <v>1971.6</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="G41" s="1">
+        <v>2091.75</v>
+      </c>
+      <c r="H41" s="1">
+        <v>2882.529999999999</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1770.08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C42" s="1">
         <v>1961.2</v>
@@ -1929,12 +2307,21 @@
         <v>2427.09</v>
       </c>
       <c r="F42" s="1">
-        <v>2566.969999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>2566.97</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2361.01</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2986.32</v>
+      </c>
+      <c r="I42" s="1">
+        <v>2848.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C43" s="1">
         <v>788.52</v>
@@ -1948,10 +2335,19 @@
       <c r="F43" s="1">
         <v>958.3</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="1">
+        <v>1113.67</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1768.78</v>
+      </c>
+      <c r="I43" s="1">
+        <v>258.66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C44" s="1">
         <v>2290.71</v>
@@ -1965,10 +2361,19 @@
       <c r="F44" s="1">
         <v>2355.79</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="1">
+        <v>3792.390000000001</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2901.509999999999</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1508.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C45" s="1">
         <v>3819.96</v>
@@ -1977,15 +2382,24 @@
         <v>3723.48</v>
       </c>
       <c r="E45" s="1">
-        <v>2821.66</v>
+        <v>2821.659999999999</v>
       </c>
       <c r="F45" s="1">
         <v>2103.75</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" s="1">
+        <v>2792.63</v>
+      </c>
+      <c r="H45" s="1">
+        <v>5391.599999999999</v>
+      </c>
+      <c r="I45" s="1">
+        <v>3849.56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C46" s="1">
         <v>3777.45</v>
@@ -1994,18 +2408,27 @@
         <v>3674.49</v>
       </c>
       <c r="E46" s="1">
-        <v>6076.409999999999</v>
+        <v>6076.41</v>
       </c>
       <c r="F46" s="1">
-        <v>4408.959999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>4408.959999999999</v>
+      </c>
+      <c r="G46" s="1">
+        <v>7136.45</v>
+      </c>
+      <c r="H46" s="1">
+        <v>6909.64</v>
+      </c>
+      <c r="I46" s="1">
+        <v>6444.929999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C47" s="1">
-        <v>637.6199999999999</v>
+        <v>637.62</v>
       </c>
       <c r="D47" s="1">
         <v>1274.87</v>
@@ -2016,10 +2439,19 @@
       <c r="F47" s="1">
         <v>1805.17</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47" s="1">
+        <v>965.1799999999999</v>
+      </c>
+      <c r="H47" s="1">
+        <v>881.5200000000001</v>
+      </c>
+      <c r="I47" s="1">
+        <v>1162.45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C48" s="1">
         <v>2955.16</v>
@@ -2033,10 +2465,19 @@
       <c r="F48" s="1">
         <v>1363.64</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="1">
+        <v>1981.85</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2470.61</v>
+      </c>
+      <c r="I48" s="1">
+        <v>2742.69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C49" s="1">
         <v>3753.26</v>
@@ -2045,15 +2486,24 @@
         <v>4077.29</v>
       </c>
       <c r="E49" s="1">
-        <v>3883.919999999999</v>
+        <v>3883.92</v>
       </c>
       <c r="F49" s="1">
-        <v>4460.429999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>4460.429999999999</v>
+      </c>
+      <c r="G49" s="1">
+        <v>4995.449999999999</v>
+      </c>
+      <c r="H49" s="1">
+        <v>5925.339999999998</v>
+      </c>
+      <c r="I49" s="1">
+        <v>5154.059999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C50" s="1">
         <v>582.9299999999999</v>
@@ -2067,10 +2517,19 @@
       <c r="F50" s="1">
         <v>704.11</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" s="1">
+        <v>675.3800000000001</v>
+      </c>
+      <c r="H50" s="1">
+        <v>432.77</v>
+      </c>
+      <c r="I50" s="1">
+        <v>740.22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C51" s="1">
         <v>2027.02</v>
@@ -2082,12 +2541,21 @@
         <v>2458.32</v>
       </c>
       <c r="F51" s="1">
-        <v>3033.099999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>3033.1</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1810.63</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2044.88</v>
+      </c>
+      <c r="I51" s="1">
+        <v>2076.11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1">
         <v>1843.96</v>
@@ -2101,10 +2569,19 @@
       <c r="F52" s="1">
         <v>2394.23</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52" s="1">
+        <v>652.24</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1551.36</v>
+      </c>
+      <c r="I52" s="1">
+        <v>2058.29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C53" s="1">
         <v>1061.62</v>
@@ -2118,10 +2595,19 @@
       <c r="F53" s="1">
         <v>1392.53</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="1">
+        <v>1598.18</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1263.16</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1200.93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C54" s="1">
         <v>317.23</v>
@@ -2135,10 +2621,19 @@
       <c r="F54" s="1">
         <v>493.18</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" s="1">
+        <v>837.33</v>
+      </c>
+      <c r="H54" s="1">
+        <v>294.07</v>
+      </c>
+      <c r="I54" s="1">
+        <v>911.99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C55" s="1">
         <v>1056.97</v>
@@ -2147,15 +2642,24 @@
         <v>543.9400000000001</v>
       </c>
       <c r="E55" s="1">
-        <v>941.5400000000001</v>
+        <v>941.54</v>
       </c>
       <c r="F55" s="1">
         <v>193.97</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="1">
+        <v>1090.28</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1598.16</v>
+      </c>
+      <c r="I55" s="1">
+        <v>465.94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C56" s="1">
         <v>592.08</v>
@@ -2169,27 +2673,45 @@
       <c r="F56" s="1">
         <v>1142.4</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="1">
+        <v>1430.52</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1162.27</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1269.36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C57" s="1">
         <v>12261.13</v>
       </c>
       <c r="D57" s="1">
-        <v>19910.96999999999</v>
+        <v>19910.97</v>
       </c>
       <c r="E57" s="1">
-        <v>19121.04</v>
+        <v>19121.03999999999</v>
       </c>
       <c r="F57" s="1">
         <v>15038.74</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" s="1">
+        <v>13148.91</v>
+      </c>
+      <c r="H57" s="1">
+        <v>10914.88</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C58" s="1">
         <v>830.51</v>
@@ -2198,15 +2720,24 @@
         <v>959.05</v>
       </c>
       <c r="E58" s="1">
-        <v>600.9000000000001</v>
+        <v>600.9</v>
       </c>
       <c r="F58" s="1">
         <v>1334.66</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="1">
+        <v>1095.7</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1063.25</v>
+      </c>
+      <c r="I58" s="1">
+        <v>1039.61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C59" s="1">
         <v>1451.97</v>
@@ -2220,10 +2751,19 @@
       <c r="F59" s="1">
         <v>1221.19</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="1">
+        <v>2688.61</v>
+      </c>
+      <c r="H59" s="1">
+        <v>559.1</v>
+      </c>
+      <c r="I59" s="1">
+        <v>842.96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C60" s="1">
         <v>513.51</v>
@@ -2237,10 +2777,19 @@
       <c r="F60" s="1">
         <v>1588.85</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="1">
+        <v>1187.74</v>
+      </c>
+      <c r="H60" s="1">
+        <v>2254.15</v>
+      </c>
+      <c r="I60" s="1">
+        <v>341.68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C61" s="1">
         <v>3005.2</v>
@@ -2249,15 +2798,24 @@
         <v>1653.93</v>
       </c>
       <c r="E61" s="1">
-        <v>3213.88</v>
+        <v>3213.879999999999</v>
       </c>
       <c r="F61" s="1">
         <v>3008.140000000001</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="1">
+        <v>2922.49</v>
+      </c>
+      <c r="H61" s="1">
+        <v>3658</v>
+      </c>
+      <c r="I61" s="1">
+        <v>4515.8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C62" s="1">
         <v>715.7</v>
@@ -2269,12 +2827,21 @@
         <v>1092.03</v>
       </c>
       <c r="F62" s="1">
-        <v>946.2800000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>946.28</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1224.18</v>
+      </c>
+      <c r="H62" s="1">
+        <v>587.3499999999999</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1479.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C63" s="1">
         <v>2872.96</v>
@@ -2288,27 +2855,45 @@
       <c r="F63" s="1">
         <v>2380.09</v>
       </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" s="1">
+        <v>2032.06</v>
+      </c>
+      <c r="H63" s="1">
+        <v>908.5200000000002</v>
+      </c>
+      <c r="I63" s="1">
+        <v>2714.59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C64" s="1">
         <v>2439.95</v>
       </c>
       <c r="D64" s="1">
-        <v>2686.019999999999</v>
+        <v>2686.02</v>
       </c>
       <c r="E64" s="1">
-        <v>3050.05</v>
+        <v>3050.049999999999</v>
       </c>
       <c r="F64" s="1">
         <v>2077.96</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64" s="1">
+        <v>2656.739999999999</v>
+      </c>
+      <c r="H64" s="1">
+        <v>3405.03</v>
+      </c>
+      <c r="I64" s="1">
+        <v>2294.77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C65" s="1">
         <v>1893.44</v>
@@ -2322,10 +2907,19 @@
       <c r="F65" s="1">
         <v>1134.77</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" s="1">
+        <v>938.64</v>
+      </c>
+      <c r="H65" s="1">
+        <v>925.0300000000001</v>
+      </c>
+      <c r="I65" s="1">
+        <v>447.54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C66" s="1">
         <v>3749.75</v>
@@ -2339,10 +2933,19 @@
       <c r="F66" s="1">
         <v>1484.76</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" s="1">
+        <v>540.73</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1550.95</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1611.54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C67" s="1">
         <v>1489.5</v>
@@ -2356,10 +2959,19 @@
       <c r="F67" s="1">
         <v>1905.2</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67" s="1">
+        <v>1762.68</v>
+      </c>
+      <c r="H67" s="1">
+        <v>845.73</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1835.21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C68" s="1">
         <v>1554.37</v>
@@ -2373,10 +2985,19 @@
       <c r="F68" s="1">
         <v>2855.139999999999</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68" s="1">
+        <v>619.6500000000001</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1668</v>
+      </c>
+      <c r="I68" s="1">
+        <v>942.7600000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C69" s="1">
         <v>1415.95</v>
@@ -2388,29 +3009,47 @@
         <v>1407.92</v>
       </c>
       <c r="F69" s="1">
-        <v>2300.059999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>2300.06</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1788.43</v>
+      </c>
+      <c r="H69" s="1">
+        <v>502.5</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1746.85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C70" s="1">
         <v>4280.41</v>
       </c>
       <c r="D70" s="1">
-        <v>4258.499999999998</v>
+        <v>4258.5</v>
       </c>
       <c r="E70" s="1">
-        <v>2873.7</v>
+        <v>2873.699999999999</v>
       </c>
       <c r="F70" s="1">
         <v>3107.05</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70" s="1">
+        <v>4782.749999999999</v>
+      </c>
+      <c r="H70" s="1">
+        <v>6819.01</v>
+      </c>
+      <c r="I70" s="1">
+        <v>4042.09</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C71" s="1">
         <v>766.38</v>
@@ -2424,10 +3063,19 @@
       <c r="F71" s="1">
         <v>198.74</v>
       </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="G71" s="1">
+        <v>826.61</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1371.63</v>
+      </c>
+      <c r="I71" s="1">
+        <v>1353.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C72" s="1">
         <v>872.77</v>
@@ -2441,10 +3089,19 @@
       <c r="F72" s="1">
         <v>918.46</v>
       </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" s="1">
+        <v>879.5899999999999</v>
+      </c>
+      <c r="H72" s="1">
+        <v>982.23</v>
+      </c>
+      <c r="I72" s="1">
+        <v>952.2499999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C73" s="1">
         <v>1500.88</v>
@@ -2458,10 +3115,19 @@
       <c r="F73" s="1">
         <v>2003.97</v>
       </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="G73" s="1">
+        <v>897.73</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1578.65</v>
+      </c>
+      <c r="I73" s="1">
+        <v>983.35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C74" s="1">
         <v>2548.3</v>
@@ -2475,10 +3141,19 @@
       <c r="F74" s="1">
         <v>2153.14</v>
       </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="G74" s="1">
+        <v>1009.96</v>
+      </c>
+      <c r="H74" s="1">
+        <v>2437.58</v>
+      </c>
+      <c r="I74" s="1">
+        <v>2187.88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C75" s="1">
         <v>772.5400000000001</v>
@@ -2492,10 +3167,19 @@
       <c r="F75" s="1">
         <v>1240.98</v>
       </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="G75" s="1">
+        <v>384.58</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1068.08</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1359.59</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C76" s="1">
         <v>2014.25</v>
@@ -2507,18 +3191,27 @@
         <v>1439.95</v>
       </c>
       <c r="F76" s="1">
-        <v>2671.35</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>2671.349999999999</v>
+      </c>
+      <c r="G76" s="1">
+        <v>3503.829999999999</v>
+      </c>
+      <c r="H76" s="1">
+        <v>4076.92</v>
+      </c>
+      <c r="I76" s="1">
+        <v>3631.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C77" s="1">
         <v>4348.49</v>
       </c>
       <c r="D77" s="1">
-        <v>4086.120000000001</v>
+        <v>4086.119999999999</v>
       </c>
       <c r="E77" s="1">
         <v>2412.38</v>
@@ -2526,10 +3219,19 @@
       <c r="F77" s="1">
         <v>3676.98</v>
       </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="G77" s="1">
+        <v>3257.27</v>
+      </c>
+      <c r="H77" s="1">
+        <v>5034.009999999997</v>
+      </c>
+      <c r="I77" s="1">
+        <v>2345.55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C78" s="1">
         <v>1474.96</v>
@@ -2543,10 +3245,19 @@
       <c r="F78" s="1">
         <v>1478.46</v>
       </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="G78" s="1">
+        <v>893.98</v>
+      </c>
+      <c r="H78" s="1">
+        <v>3096.3</v>
+      </c>
+      <c r="I78" s="1">
+        <v>955.1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C79" s="1">
         <v>2378.14</v>
@@ -2560,10 +3271,19 @@
       <c r="F79" s="1">
         <v>2295.31</v>
       </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="G79" s="1">
+        <v>1711.35</v>
+      </c>
+      <c r="H79" s="1">
+        <v>2764.51</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1230.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C80" s="1">
         <v>1376.44</v>
@@ -2572,18 +3292,27 @@
         <v>1138.85</v>
       </c>
       <c r="E80" s="1">
-        <v>355.83</v>
+        <v>355.8299999999999</v>
       </c>
       <c r="F80" s="1">
-        <v>724.1200000000001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>724.12</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2067.91</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1289</v>
+      </c>
+      <c r="I80" s="1">
+        <v>997.27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C81" s="1">
-        <v>919.64</v>
+        <v>919.6400000000001</v>
       </c>
       <c r="D81" s="1">
         <v>1501.93</v>
@@ -2594,10 +3323,19 @@
       <c r="F81" s="1">
         <v>1509.81</v>
       </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="G81" s="1">
+        <v>1421.33</v>
+      </c>
+      <c r="H81" s="1">
+        <v>1483.11</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1657.01</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C82" s="1">
         <v>2162.61</v>
@@ -2611,16 +3349,25 @@
       <c r="F82" s="1">
         <v>447.98</v>
       </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="G82" s="1">
+        <v>1648.58</v>
+      </c>
+      <c r="H82" s="1">
+        <v>2107.74</v>
+      </c>
+      <c r="I82" s="1">
+        <v>2839.939999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C83" s="1">
         <v>377.4000000000001</v>
       </c>
       <c r="D83" s="1">
-        <v>580.7199999999999</v>
+        <v>580.72</v>
       </c>
       <c r="E83" s="1">
         <v>1681.22</v>
@@ -2628,10 +3375,19 @@
       <c r="F83" s="1">
         <v>1817.46</v>
       </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="G83" s="1">
+        <v>805.59</v>
+      </c>
+      <c r="H83" s="1">
+        <v>543.6</v>
+      </c>
+      <c r="I83" s="1">
+        <v>1402.55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C84" s="1">
         <v>1070.29</v>
@@ -2643,12 +3399,21 @@
         <v>396.9000000000001</v>
       </c>
       <c r="F84" s="1">
-        <v>2572.029999999999</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+        <v>2572.03</v>
+      </c>
+      <c r="G84" s="1">
+        <v>2155.11</v>
+      </c>
+      <c r="H84" s="1">
+        <v>1778.45</v>
+      </c>
+      <c r="I84" s="1">
+        <v>1643.54</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C85" s="1">
         <v>7074.939999999999</v>
@@ -2660,12 +3425,21 @@
         <v>5055.36</v>
       </c>
       <c r="F85" s="1">
-        <v>6339.08</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+        <v>6339.079999999999</v>
+      </c>
+      <c r="G85" s="1">
+        <v>5621.51</v>
+      </c>
+      <c r="H85" s="1">
+        <v>8947.429999999997</v>
+      </c>
+      <c r="I85" s="1">
+        <v>8337.23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C86" s="1">
         <v>3901.26</v>
@@ -2679,10 +3453,19 @@
       <c r="F86" s="1">
         <v>1635.89</v>
       </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="G86" s="1">
+        <v>1522.44</v>
+      </c>
+      <c r="H86" s="1">
+        <v>1818.16</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1766.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C87" s="1">
         <v>338.96</v>
@@ -2696,10 +3479,19 @@
       <c r="F87" s="1">
         <v>1308.56</v>
       </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="G87" s="1">
+        <v>636.6700000000001</v>
+      </c>
+      <c r="H87" s="1">
+        <v>1116.94</v>
+      </c>
+      <c r="I87" s="1">
+        <v>476.95</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C88" s="1">
         <v>731.25</v>
@@ -2713,10 +3505,19 @@
       <c r="F88" s="1">
         <v>682.9400000000001</v>
       </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="G88" s="1">
+        <v>374.64</v>
+      </c>
+      <c r="H88" s="1">
+        <v>1754.5</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C89" s="1">
         <v>1780.59</v>
@@ -2730,27 +3531,45 @@
       <c r="F89" s="1">
         <v>838.25</v>
       </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="G89" s="1">
+        <v>443.85</v>
+      </c>
+      <c r="H89" s="1">
+        <v>773.52</v>
+      </c>
+      <c r="I89" s="1">
+        <v>777.72</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C90" s="1">
-        <v>4043.509999999999</v>
+        <v>4043.51</v>
       </c>
       <c r="D90" s="1">
         <v>2354.11</v>
       </c>
       <c r="E90" s="1">
-        <v>3138.919999999999</v>
+        <v>3138.92</v>
       </c>
       <c r="F90" s="1">
-        <v>4355.07</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+        <v>4355.070000000001</v>
+      </c>
+      <c r="G90" s="1">
+        <v>3160.359999999999</v>
+      </c>
+      <c r="H90" s="1">
+        <v>3639.469999999999</v>
+      </c>
+      <c r="I90" s="1">
+        <v>3163.79</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C91" s="1">
         <v>1934.44</v>
@@ -2759,15 +3578,24 @@
         <v>2170.67</v>
       </c>
       <c r="E91" s="1">
-        <v>3081.8</v>
+        <v>3081.799999999999</v>
       </c>
       <c r="F91" s="1">
         <v>1728.84</v>
       </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="G91" s="1">
+        <v>1223.49</v>
+      </c>
+      <c r="H91" s="1">
+        <v>2187.09</v>
+      </c>
+      <c r="I91" s="1">
+        <v>1336.31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C92" s="1">
         <v>2267.17</v>
@@ -2779,12 +3607,21 @@
         <v>1292.31</v>
       </c>
       <c r="F92" s="1">
-        <v>3350.690000000001</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+        <v>3350.69</v>
+      </c>
+      <c r="G92" s="1">
+        <v>1124.65</v>
+      </c>
+      <c r="H92" s="1">
+        <v>2275.4</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1361.47</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C93" s="1">
         <v>651.77</v>
@@ -2796,12 +3633,21 @@
         <v>1279.15</v>
       </c>
       <c r="F93" s="1">
-        <v>664.8399999999999</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+        <v>664.84</v>
+      </c>
+      <c r="G93" s="1">
+        <v>199.55</v>
+      </c>
+      <c r="H93" s="1">
+        <v>507.83</v>
+      </c>
+      <c r="I93" s="1">
+        <v>797.0599999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C94" s="1">
         <v>3366.97</v>
@@ -2815,10 +3661,19 @@
       <c r="F94" s="1">
         <v>2468.15</v>
       </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="G94" s="1">
+        <v>1701.1</v>
+      </c>
+      <c r="H94" s="1">
+        <v>2134.39</v>
+      </c>
+      <c r="I94" s="1">
+        <v>3370.879999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C95" s="1">
         <v>3336.71</v>
@@ -2832,10 +3687,19 @@
       <c r="F95" s="1">
         <v>2734.49</v>
       </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="G95" s="1">
+        <v>4299.229999999999</v>
+      </c>
+      <c r="H95" s="1">
+        <v>4061.71</v>
+      </c>
+      <c r="I95" s="1">
+        <v>2590.25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C96" s="1">
         <v>2228.38</v>
@@ -2849,27 +3713,45 @@
       <c r="F96" s="1">
         <v>2392.38</v>
       </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="G96" s="1">
+        <v>777.54</v>
+      </c>
+      <c r="H96" s="1">
+        <v>4604.91</v>
+      </c>
+      <c r="I96" s="1">
+        <v>1777.6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C97" s="1">
         <v>1021.31</v>
       </c>
       <c r="D97" s="1">
-        <v>3722.439999999999</v>
+        <v>3722.44</v>
       </c>
       <c r="E97" s="1">
-        <v>3038.649999999999</v>
+        <v>3038.650000000001</v>
       </c>
       <c r="F97" s="1">
         <v>2186.38</v>
       </c>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="G97" s="1">
+        <v>469.4300000000001</v>
+      </c>
+      <c r="H97" s="1">
+        <v>2216.95</v>
+      </c>
+      <c r="I97" s="1">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C98" s="1">
         <v>1068.52</v>
@@ -2883,10 +3765,19 @@
       <c r="F98" s="1">
         <v>461.08</v>
       </c>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="G98" s="1">
+        <v>818.1900000000001</v>
+      </c>
+      <c r="H98" s="1">
+        <v>1161.09</v>
+      </c>
+      <c r="I98" s="1">
+        <v>1568.55</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C99" s="1">
         <v>1999.22</v>
@@ -2900,10 +3791,19 @@
       <c r="F99" s="1">
         <v>1099.66</v>
       </c>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="G99" s="1">
+        <v>2253.02</v>
+      </c>
+      <c r="H99" s="1">
+        <v>2762.91</v>
+      </c>
+      <c r="I99" s="1">
+        <v>1358.07</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C100" s="1">
         <v>1331.28</v>
@@ -2917,10 +3817,19 @@
       <c r="F100" s="1">
         <v>198.8</v>
       </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="G100" s="1">
+        <v>401.07</v>
+      </c>
+      <c r="H100" s="1">
+        <v>2164.31</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C101" s="1">
         <v>1478.85</v>
@@ -2934,10 +3843,19 @@
       <c r="F101" s="1">
         <v>1556.88</v>
       </c>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="G101" s="1">
+        <v>947.9400000000001</v>
+      </c>
+      <c r="H101" s="1">
+        <v>2387.059999999999</v>
+      </c>
+      <c r="I101" s="1">
+        <v>1564.75</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C102" s="1">
         <v>2610.559999999999</v>
@@ -2951,10 +3869,19 @@
       <c r="F102" s="1">
         <v>1717.61</v>
       </c>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="G102" s="1">
+        <v>2553.159999999999</v>
+      </c>
+      <c r="H102" s="1">
+        <v>2130.59</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1980.78</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C103" s="1">
         <v>851.6</v>
@@ -2968,10 +3895,19 @@
       <c r="F103" s="1">
         <v>878.9000000000001</v>
       </c>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="G103" s="1">
+        <v>1071.08</v>
+      </c>
+      <c r="H103" s="1">
+        <v>2046.37</v>
+      </c>
+      <c r="I103" s="1">
+        <v>1030.87</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C104" s="1">
         <v>2527.389999999999</v>
@@ -2980,15 +3916,24 @@
         <v>2643.91</v>
       </c>
       <c r="E104" s="1">
-        <v>881.6500000000001</v>
+        <v>881.65</v>
       </c>
       <c r="F104" s="1">
         <v>1037.36</v>
       </c>
-    </row>
-    <row r="105" spans="1:6">
+      <c r="G104" s="1">
+        <v>1577.83</v>
+      </c>
+      <c r="H104" s="1">
+        <v>1536.26</v>
+      </c>
+      <c r="I104" s="1">
+        <v>1325.58</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C105" s="1">
         <v>1402.23</v>
@@ -3002,13 +3947,22 @@
       <c r="F105" s="1">
         <v>3017.93</v>
       </c>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="G105" s="1">
+        <v>584.25</v>
+      </c>
+      <c r="H105" s="1">
+        <v>4544.6</v>
+      </c>
+      <c r="I105" s="1">
+        <v>2239.1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C106" s="1">
-        <v>3101.879999999999</v>
+        <v>3101.88</v>
       </c>
       <c r="D106" s="1">
         <v>1939.38</v>
@@ -3019,10 +3973,19 @@
       <c r="F106" s="1">
         <v>1094.45</v>
       </c>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="G106" s="1">
+        <v>2037.78</v>
+      </c>
+      <c r="H106" s="1">
+        <v>1875.9</v>
+      </c>
+      <c r="I106" s="1">
+        <v>1145.33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C107" s="1">
         <v>965.5700000000001</v>
@@ -3036,10 +3999,19 @@
       <c r="F107" s="1">
         <v>939.04</v>
       </c>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="G107" s="1">
+        <v>1279.73</v>
+      </c>
+      <c r="H107" s="1">
+        <v>1618.53</v>
+      </c>
+      <c r="I107" s="1">
+        <v>1136.74</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C108" s="1">
         <v>1591.46</v>
@@ -3053,10 +4025,19 @@
       <c r="F108" s="1">
         <v>1211.3</v>
       </c>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="G108" s="1">
+        <v>1177.2</v>
+      </c>
+      <c r="H108" s="1">
+        <v>3278.88</v>
+      </c>
+      <c r="I108" s="1">
+        <v>2080.28</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C109" s="1">
         <v>1718.56</v>
@@ -3070,10 +4051,19 @@
       <c r="F109" s="1">
         <v>1415.53</v>
       </c>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="G109" s="1">
+        <v>1446.36</v>
+      </c>
+      <c r="H109" s="1">
+        <v>3098.919999999999</v>
+      </c>
+      <c r="I109" s="1">
+        <v>2221.889999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C110" s="1">
         <v>758.08</v>
@@ -3087,10 +4077,19 @@
       <c r="F110" s="1">
         <v>1149.59</v>
       </c>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="G110" s="1">
+        <v>776.75</v>
+      </c>
+      <c r="H110" s="1">
+        <v>979.15</v>
+      </c>
+      <c r="I110" s="1">
+        <v>1006.22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C111" s="1">
         <v>1064.7</v>
@@ -3104,10 +4103,19 @@
       <c r="F111" s="1">
         <v>1849.46</v>
       </c>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="G111" s="1">
+        <v>435.53</v>
+      </c>
+      <c r="H111" s="1">
+        <v>1332.91</v>
+      </c>
+      <c r="I111" s="1">
+        <v>1200.44</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C112" s="1">
         <v>1395.99</v>
@@ -3121,10 +4129,19 @@
       <c r="F112" s="1">
         <v>2532.33</v>
       </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="G112" s="1">
+        <v>2251.05</v>
+      </c>
+      <c r="H112" s="1">
+        <v>1233.34</v>
+      </c>
+      <c r="I112" s="1">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C113" s="1">
         <v>1175.47</v>
@@ -3138,16 +4155,25 @@
       <c r="F113" s="1">
         <v>1437.51</v>
       </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" s="1">
+        <v>1993.46</v>
+      </c>
+      <c r="H113" s="1">
+        <v>1420.34</v>
+      </c>
+      <c r="I113" s="1">
+        <v>1134.07</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C114" s="1">
         <v>822.8900000000001</v>
       </c>
       <c r="D114" s="1">
-        <v>859.42</v>
+        <v>859.4200000000001</v>
       </c>
       <c r="E114" s="1">
         <v>1437.1</v>
@@ -3155,10 +4181,19 @@
       <c r="F114" s="1">
         <v>1785.19</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" s="1">
+        <v>50.99</v>
+      </c>
+      <c r="H114" s="1">
+        <v>2051.07</v>
+      </c>
+      <c r="I114" s="1">
+        <v>1251.61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C115" s="1">
         <v>1404.71</v>
@@ -3172,10 +4207,19 @@
       <c r="F115" s="1">
         <v>347.96</v>
       </c>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="G115" s="1">
+        <v>1240.58</v>
+      </c>
+      <c r="H115" s="1">
+        <v>1030.05</v>
+      </c>
+      <c r="I115" s="1">
+        <v>951.8299999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C116" s="1">
         <v>2105.71</v>
@@ -3189,10 +4233,19 @@
       <c r="F116" s="1">
         <v>2121.22</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" s="1">
+        <v>1841.7</v>
+      </c>
+      <c r="H116" s="1">
+        <v>1380.07</v>
+      </c>
+      <c r="I116" s="1">
+        <v>1819.1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C117" s="1">
         <v>1977.4</v>
@@ -3206,33 +4259,51 @@
       <c r="F117" s="1">
         <v>1984.12</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="G117" s="1">
+        <v>1826.83</v>
+      </c>
+      <c r="H117" s="1">
+        <v>1191.7</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C118" s="1">
         <v>4501.04</v>
       </c>
       <c r="D118" s="1">
-        <v>4681.839999999999</v>
+        <v>4681.84</v>
       </c>
       <c r="E118" s="1">
-        <v>4462.96</v>
+        <v>4462.960000000001</v>
       </c>
       <c r="F118" s="1">
         <v>2237.84</v>
       </c>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="G118" s="1">
+        <v>3346.46</v>
+      </c>
+      <c r="H118" s="1">
+        <v>2780.62</v>
+      </c>
+      <c r="I118" s="1">
+        <v>5790.379999999998</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C119" s="1">
         <v>413.96</v>
       </c>
       <c r="D119" s="1">
-        <v>634.61</v>
+        <v>634.6099999999999</v>
       </c>
       <c r="E119" s="1">
         <v>326.85</v>
@@ -3240,13 +4311,22 @@
       <c r="F119" s="1">
         <v>1517.56</v>
       </c>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="G119" s="1">
+        <v>935.52</v>
+      </c>
+      <c r="H119" s="1">
+        <v>602.13</v>
+      </c>
+      <c r="I119" s="1">
+        <v>786.9200000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C120" s="1">
-        <v>947.28</v>
+        <v>947.2800000000001</v>
       </c>
       <c r="D120" s="1">
         <v>2070.29</v>
@@ -3257,10 +4337,19 @@
       <c r="F120" s="1">
         <v>1014.17</v>
       </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="G120" s="1">
+        <v>1243.8</v>
+      </c>
+      <c r="H120" s="1">
+        <v>2669.99</v>
+      </c>
+      <c r="I120" s="1">
+        <v>1268.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C121" s="1">
         <v>2646.02</v>
@@ -3274,10 +4363,19 @@
       <c r="F121" s="1">
         <v>1992.7</v>
       </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" s="1">
+        <v>1107.13</v>
+      </c>
+      <c r="H121" s="1">
+        <v>1691.63</v>
+      </c>
+      <c r="I121" s="1">
+        <v>2011.15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C122" s="1">
         <v>1552.55</v>
@@ -3291,10 +4389,19 @@
       <c r="F122" s="1">
         <v>2699.1</v>
       </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="G122" s="1">
+        <v>1847.73</v>
+      </c>
+      <c r="H122" s="1">
+        <v>1773.39</v>
+      </c>
+      <c r="I122" s="1">
+        <v>1470.71</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C123" s="1">
         <v>1194.42</v>
@@ -3308,10 +4415,19 @@
       <c r="F123" s="1">
         <v>1689.47</v>
       </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="G123" s="1">
+        <v>2676.34</v>
+      </c>
+      <c r="H123" s="1">
+        <v>1901.21</v>
+      </c>
+      <c r="I123" s="1">
+        <v>2314.56</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C124" s="1">
         <v>3174.419999999999</v>
@@ -3325,27 +4441,45 @@
       <c r="F124" s="1">
         <v>2551.11</v>
       </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="G124" s="1">
+        <v>2780.91</v>
+      </c>
+      <c r="H124" s="1">
+        <v>2585.849999999999</v>
+      </c>
+      <c r="I124" s="1">
+        <v>2542.99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C125" s="1">
         <v>1343.44</v>
       </c>
       <c r="D125" s="1">
-        <v>2697.94</v>
+        <v>2697.939999999999</v>
       </c>
       <c r="E125" s="1">
-        <v>3069.38</v>
+        <v>3069.379999999999</v>
       </c>
       <c r="F125" s="1">
-        <v>2885.4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+        <v>2885.400000000001</v>
+      </c>
+      <c r="G125" s="1">
+        <v>1327.67</v>
+      </c>
+      <c r="H125" s="1">
+        <v>4439.32</v>
+      </c>
+      <c r="I125" s="1">
+        <v>1894.51</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C126" s="1">
         <v>1266.23</v>
@@ -3359,16 +4493,25 @@
       <c r="F126" s="1">
         <v>1812.42</v>
       </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="G126" s="1">
+        <v>2930.99</v>
+      </c>
+      <c r="H126" s="1">
+        <v>553.62</v>
+      </c>
+      <c r="I126" s="1">
+        <v>1260.49</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C127" s="1">
         <v>1864.5</v>
       </c>
       <c r="D127" s="1">
-        <v>826.28</v>
+        <v>826.2800000000001</v>
       </c>
       <c r="E127" s="1">
         <v>337.16</v>
@@ -3376,10 +4519,19 @@
       <c r="F127" s="1">
         <v>1247.98</v>
       </c>
-    </row>
-    <row r="128" spans="1:6">
+      <c r="G127" s="1">
+        <v>1984.89</v>
+      </c>
+      <c r="H127" s="1">
+        <v>1571.21</v>
+      </c>
+      <c r="I127" s="1">
+        <v>1190.05</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C128" s="1">
         <v>1999.92</v>
@@ -3393,16 +4545,25 @@
       <c r="F128" s="1">
         <v>2202.19</v>
       </c>
-    </row>
-    <row r="129" spans="1:6">
+      <c r="G128" s="1">
+        <v>2210.98</v>
+      </c>
+      <c r="H128" s="1">
+        <v>3626.68</v>
+      </c>
+      <c r="I128" s="1">
+        <v>2512.639999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C129" s="1">
-        <v>3685.01</v>
+        <v>3685.009999999999</v>
       </c>
       <c r="D129" s="1">
-        <v>3129.409999999999</v>
+        <v>3129.41</v>
       </c>
       <c r="E129" s="1">
         <v>3139.79</v>
@@ -3410,10 +4571,19 @@
       <c r="F129" s="1">
         <v>3725.99</v>
       </c>
-    </row>
-    <row r="130" spans="1:6">
+      <c r="G129" s="1">
+        <v>3474.58</v>
+      </c>
+      <c r="H129" s="1">
+        <v>6656.269999999998</v>
+      </c>
+      <c r="I129" s="1">
+        <v>4252.95</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C130" s="1">
         <v>983.34</v>
@@ -3427,16 +4597,25 @@
       <c r="F130" s="1">
         <v>1911.44</v>
       </c>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="G130" s="1">
+        <v>1621.18</v>
+      </c>
+      <c r="H130" s="1">
+        <v>3157.7</v>
+      </c>
+      <c r="I130" s="1">
+        <v>916.7800000000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C131" s="1">
         <v>1339.4</v>
       </c>
       <c r="D131" s="1">
-        <v>499.9399999999999</v>
+        <v>499.94</v>
       </c>
       <c r="E131" s="1">
         <v>519.9399999999999</v>
@@ -3444,10 +4623,19 @@
       <c r="F131" s="1">
         <v>901.5900000000001</v>
       </c>
-    </row>
-    <row r="132" spans="1:6">
+      <c r="G131" s="1">
+        <v>282.41</v>
+      </c>
+      <c r="H131" s="1">
+        <v>733.6</v>
+      </c>
+      <c r="I131" s="1">
+        <v>908.09</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C132" s="1">
         <v>1912.55</v>
@@ -3456,15 +4644,24 @@
         <v>2230.21</v>
       </c>
       <c r="E132" s="1">
-        <v>4328.57</v>
+        <v>4328.569999999999</v>
       </c>
       <c r="F132" s="1">
         <v>2945.78</v>
       </c>
-    </row>
-    <row r="133" spans="1:6">
+      <c r="G132" s="1">
+        <v>3464.400000000001</v>
+      </c>
+      <c r="H132" s="1">
+        <v>3592.659999999999</v>
+      </c>
+      <c r="I132" s="1">
+        <v>2716.75</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C133" s="1">
         <v>2439.88</v>
@@ -3473,15 +4670,24 @@
         <v>3253.28</v>
       </c>
       <c r="E133" s="1">
-        <v>4225.360000000001</v>
+        <v>4225.36</v>
       </c>
       <c r="F133" s="1">
-        <v>2584.309999999999</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
+        <v>2584.31</v>
+      </c>
+      <c r="G133" s="1">
+        <v>2782.34</v>
+      </c>
+      <c r="H133" s="1">
+        <v>2931.42</v>
+      </c>
+      <c r="I133" s="1">
+        <v>2406.7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C134" s="1">
         <v>2629.67</v>
@@ -3495,10 +4701,19 @@
       <c r="F134" s="1">
         <v>1466.2</v>
       </c>
-    </row>
-    <row r="135" spans="1:6">
+      <c r="G134" s="1">
+        <v>2264.11</v>
+      </c>
+      <c r="H134" s="1">
+        <v>1626.36</v>
+      </c>
+      <c r="I134" s="1">
+        <v>1771.06</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C135" s="1">
         <v>1956.15</v>
@@ -3510,12 +4725,21 @@
         <v>1055.67</v>
       </c>
       <c r="F135" s="1">
-        <v>2275.19</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>2275.190000000001</v>
+      </c>
+      <c r="G135" s="1">
+        <v>2516.92</v>
+      </c>
+      <c r="H135" s="1">
+        <v>1682.56</v>
+      </c>
+      <c r="I135" s="1">
+        <v>3202.349999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C136" s="1">
         <v>1342.66</v>
@@ -3529,10 +4753,19 @@
       <c r="F136" s="1">
         <v>1230.67</v>
       </c>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="G136" s="1">
+        <v>444.67</v>
+      </c>
+      <c r="H136" s="1">
+        <v>1403.83</v>
+      </c>
+      <c r="I136" s="1">
+        <v>397.96</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C137" s="1">
         <v>3321.04</v>
@@ -3546,13 +4779,22 @@
       <c r="F137" s="1">
         <v>3162.309999999999</v>
       </c>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="G137" s="1">
+        <v>2901.78</v>
+      </c>
+      <c r="H137" s="1">
+        <v>4771.34</v>
+      </c>
+      <c r="I137" s="1">
+        <v>2621.37</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C138" s="1">
-        <v>2586.709999999999</v>
+        <v>2586.71</v>
       </c>
       <c r="D138" s="1">
         <v>1069.26</v>
@@ -3563,10 +4805,19 @@
       <c r="F138" s="1">
         <v>1548.42</v>
       </c>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="G138" s="1">
+        <v>2218.86</v>
+      </c>
+      <c r="H138" s="1">
+        <v>1768.74</v>
+      </c>
+      <c r="I138" s="1">
+        <v>2364.51</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C139" s="1">
         <v>2613.27</v>
@@ -3580,27 +4831,45 @@
       <c r="F139" s="1">
         <v>2905.149999999999</v>
       </c>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="G139" s="1">
+        <v>1413.88</v>
+      </c>
+      <c r="H139" s="1">
+        <v>2636.929999999999</v>
+      </c>
+      <c r="I139" s="1">
+        <v>1417.64</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C140" s="1">
-        <v>2938.319999999999</v>
+        <v>2938.32</v>
       </c>
       <c r="D140" s="1">
-        <v>4053.659999999999</v>
+        <v>4053.66</v>
       </c>
       <c r="E140" s="1">
-        <v>2615.400000000001</v>
+        <v>2615.4</v>
       </c>
       <c r="F140" s="1">
         <v>2041.12</v>
       </c>
-    </row>
-    <row r="141" spans="1:6">
+      <c r="G140" s="1">
+        <v>1492.7</v>
+      </c>
+      <c r="H140" s="1">
+        <v>5391.519999999999</v>
+      </c>
+      <c r="I140" s="1">
+        <v>2447.580000000001</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C141" s="1">
         <v>2448.8</v>
@@ -3614,10 +4883,19 @@
       <c r="F141" s="1">
         <v>1995.12</v>
       </c>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="G141" s="1">
+        <v>2036.93</v>
+      </c>
+      <c r="H141" s="1">
+        <v>4126.329999999999</v>
+      </c>
+      <c r="I141" s="1">
+        <v>2525.51</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C142" s="1">
         <v>1494.82</v>
@@ -3631,10 +4909,19 @@
       <c r="F142" s="1">
         <v>963.9200000000001</v>
       </c>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="G142" s="1">
+        <v>2042.97</v>
+      </c>
+      <c r="H142" s="1">
+        <v>2448.34</v>
+      </c>
+      <c r="I142" s="1">
+        <v>1325.48</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C143" s="1">
         <v>1179.32</v>
@@ -3643,32 +4930,50 @@
         <v>32.99</v>
       </c>
       <c r="E143" s="1">
-        <v>440.1899999999999</v>
+        <v>440.19</v>
       </c>
       <c r="F143" s="1">
         <v>1009.16</v>
       </c>
-    </row>
-    <row r="144" spans="1:6">
+      <c r="G143" s="1">
+        <v>898.22</v>
+      </c>
+      <c r="H143" s="1">
+        <v>527.45</v>
+      </c>
+      <c r="I143" s="1">
+        <v>567.73</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C144" s="1">
         <v>1737.23</v>
       </c>
       <c r="D144" s="1">
-        <v>885.04</v>
+        <v>885.0400000000001</v>
       </c>
       <c r="E144" s="1">
-        <v>2330.150000000001</v>
+        <v>2330.15</v>
       </c>
       <c r="F144" s="1">
         <v>1882.68</v>
       </c>
-    </row>
-    <row r="145" spans="1:6">
+      <c r="G144" s="1">
+        <v>1224.21</v>
+      </c>
+      <c r="H144" s="1">
+        <v>3708.689999999999</v>
+      </c>
+      <c r="I144" s="1">
+        <v>1946.98</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C145" s="1">
         <v>249.47</v>
@@ -3677,15 +4982,24 @@
         <v>476.71</v>
       </c>
       <c r="E145" s="1">
-        <v>808.7</v>
+        <v>808.6999999999998</v>
       </c>
       <c r="F145" s="1">
         <v>1216.97</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
+      <c r="G145" s="1">
+        <v>543.6200000000001</v>
+      </c>
+      <c r="H145" s="1">
+        <v>953.47</v>
+      </c>
+      <c r="I145" s="1">
+        <v>270.09</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C146" s="1">
         <v>246.38</v>
@@ -3699,10 +5013,19 @@
       <c r="F146" s="1">
         <v>729.2</v>
       </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="G146" s="1">
+        <v>469.11</v>
+      </c>
+      <c r="H146" s="1">
+        <v>743.3000000000002</v>
+      </c>
+      <c r="I146" s="1">
+        <v>418.3099999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C147" s="1">
         <v>2091.59</v>
@@ -3716,10 +5039,19 @@
       <c r="F147" s="1">
         <v>2845.87</v>
       </c>
-    </row>
-    <row r="148" spans="1:6">
+      <c r="G147" s="1">
+        <v>1573.23</v>
+      </c>
+      <c r="H147" s="1">
+        <v>2023.69</v>
+      </c>
+      <c r="I147" s="1">
+        <v>1503.69</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C148" s="1">
         <v>945.6</v>
@@ -3733,13 +5065,22 @@
       <c r="F148" s="1">
         <v>1399.68</v>
       </c>
-    </row>
-    <row r="149" spans="1:6">
+      <c r="G148" s="1">
+        <v>934.3099999999999</v>
+      </c>
+      <c r="H148" s="1">
+        <v>991.33</v>
+      </c>
+      <c r="I148" s="1">
+        <v>897.1400000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C149" s="1">
-        <v>5156.8</v>
+        <v>5156.799999999999</v>
       </c>
       <c r="D149" s="1">
         <v>2052.92</v>
@@ -3750,13 +5091,22 @@
       <c r="F149" s="1">
         <v>2116.42</v>
       </c>
-    </row>
-    <row r="150" spans="1:6">
+      <c r="G149" s="1">
+        <v>2069.79</v>
+      </c>
+      <c r="H149" s="1">
+        <v>4631.27</v>
+      </c>
+      <c r="I149" s="1">
+        <v>4364.81</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C150" s="1">
-        <v>563.86</v>
+        <v>563.8599999999999</v>
       </c>
       <c r="D150" s="1">
         <v>144.97</v>
@@ -3767,13 +5117,22 @@
       <c r="F150" s="1">
         <v>479.23</v>
       </c>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="G150" s="1">
+        <v>770.64</v>
+      </c>
+      <c r="H150" s="1">
+        <v>845.3</v>
+      </c>
+      <c r="I150" s="1">
+        <v>678.26</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C151" s="1">
-        <v>3157.129999999999</v>
+        <v>3157.13</v>
       </c>
       <c r="D151" s="1">
         <v>3956.639999999999</v>
@@ -3782,12 +5141,21 @@
         <v>3324.73</v>
       </c>
       <c r="F151" s="1">
-        <v>2937.329999999999</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
+        <v>2937.330000000001</v>
+      </c>
+      <c r="G151" s="1">
+        <v>2724.7</v>
+      </c>
+      <c r="H151" s="1">
+        <v>5161.089999999998</v>
+      </c>
+      <c r="I151" s="1">
+        <v>3440.429999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C152" s="1">
         <v>1931.53</v>
@@ -3796,15 +5164,24 @@
         <v>1721.64</v>
       </c>
       <c r="E152" s="1">
-        <v>2393.449999999999</v>
+        <v>2393.45</v>
       </c>
       <c r="F152" s="1">
         <v>1932.46</v>
       </c>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="G152" s="1">
+        <v>1545.5</v>
+      </c>
+      <c r="H152" s="1">
+        <v>2687.04</v>
+      </c>
+      <c r="I152" s="1">
+        <v>2778.26</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C153" s="1">
         <v>3122.129999999999</v>
@@ -3818,10 +5195,19 @@
       <c r="F153" s="1">
         <v>1899.86</v>
       </c>
-    </row>
-    <row r="154" spans="1:6">
+      <c r="G153" s="1">
+        <v>783</v>
+      </c>
+      <c r="H153" s="1">
+        <v>2495.559999999999</v>
+      </c>
+      <c r="I153" s="1">
+        <v>1387.35</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C154" s="1">
         <v>2558.16</v>
@@ -3835,30 +5221,48 @@
       <c r="F154" s="1">
         <v>3988.159999999999</v>
       </c>
-    </row>
-    <row r="155" spans="1:6">
+      <c r="G154" s="1">
+        <v>2554.87</v>
+      </c>
+      <c r="H154" s="1">
+        <v>3966.75</v>
+      </c>
+      <c r="I154" s="1">
+        <v>7005.389999999998</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C155" s="1">
         <v>6759.990000000002</v>
       </c>
       <c r="D155" s="1">
-        <v>4435.52</v>
+        <v>4435.519999999999</v>
       </c>
       <c r="E155" s="1">
-        <v>3889.879999999999</v>
+        <v>3889.879999999998</v>
       </c>
       <c r="F155" s="1">
         <v>2341.5</v>
       </c>
-    </row>
-    <row r="156" spans="1:6">
+      <c r="G155" s="1">
+        <v>3476.96</v>
+      </c>
+      <c r="H155" s="1">
+        <v>2063.21</v>
+      </c>
+      <c r="I155" s="1">
+        <v>2294.25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C156" s="1">
-        <v>3049.51</v>
+        <v>3049.509999999999</v>
       </c>
       <c r="D156" s="1">
         <v>1690.67</v>
@@ -3869,10 +5273,19 @@
       <c r="F156" s="1">
         <v>2233.09</v>
       </c>
-    </row>
-    <row r="157" spans="1:6">
+      <c r="G156" s="1">
+        <v>2610.04</v>
+      </c>
+      <c r="H156" s="1">
+        <v>3300.399999999999</v>
+      </c>
+      <c r="I156" s="1">
+        <v>2767.48</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C157" s="1">
         <v>1998.64</v>
@@ -3886,13 +5299,22 @@
       <c r="F157" s="1">
         <v>2153.02</v>
       </c>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="G157" s="1">
+        <v>719.8000000000002</v>
+      </c>
+      <c r="H157" s="1">
+        <v>1606.27</v>
+      </c>
+      <c r="I157" s="1">
+        <v>1354.72</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C158" s="1">
-        <v>735.8000000000002</v>
+        <v>735.8</v>
       </c>
       <c r="D158" s="1">
         <v>1580</v>
@@ -3903,10 +5325,19 @@
       <c r="F158" s="1">
         <v>1670.43</v>
       </c>
-    </row>
-    <row r="159" spans="1:6">
+      <c r="G158" s="1">
+        <v>1769.76</v>
+      </c>
+      <c r="H158" s="1">
+        <v>956.0599999999999</v>
+      </c>
+      <c r="I158" s="1">
+        <v>1046.86</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C159" s="1">
         <v>2182.87</v>
@@ -3920,10 +5351,19 @@
       <c r="F159" s="1">
         <v>1092.32</v>
       </c>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="G159" s="1">
+        <v>1435.54</v>
+      </c>
+      <c r="H159" s="1">
+        <v>1462.06</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C160" s="1">
         <v>2228.86</v>
@@ -3932,18 +5372,27 @@
         <v>3076.01</v>
       </c>
       <c r="E160" s="1">
-        <v>4183.33</v>
+        <v>4183.330000000001</v>
       </c>
       <c r="F160" s="1">
         <v>4969.679999999999</v>
       </c>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="G160" s="1">
+        <v>2962.189999999999</v>
+      </c>
+      <c r="H160" s="1">
+        <v>2396.76</v>
+      </c>
+      <c r="I160" s="1">
+        <v>2847.72</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C161" s="1">
-        <v>2697.429999999999</v>
+        <v>2697.43</v>
       </c>
       <c r="D161" s="1">
         <v>3256.04</v>
@@ -3952,12 +5401,21 @@
         <v>2154.03</v>
       </c>
       <c r="F161" s="1">
-        <v>2771.679999999999</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
+        <v>2771.68</v>
+      </c>
+      <c r="G161" s="1">
+        <v>1801.27</v>
+      </c>
+      <c r="H161" s="1">
+        <v>1635.09</v>
+      </c>
+      <c r="I161" s="1">
+        <v>3054.709999999999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C162" s="1">
         <v>2325.62</v>
@@ -3971,10 +5429,19 @@
       <c r="F162" s="1">
         <v>801.9200000000001</v>
       </c>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="G162" s="1">
+        <v>1153.87</v>
+      </c>
+      <c r="H162" s="1">
+        <v>1471.11</v>
+      </c>
+      <c r="I162" s="1">
+        <v>1622.35</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C163" s="1">
         <v>2890.15</v>
@@ -3988,10 +5455,19 @@
       <c r="F163" s="1">
         <v>1511.62</v>
       </c>
-    </row>
-    <row r="164" spans="1:6">
+      <c r="G163" s="1">
+        <v>1713.17</v>
+      </c>
+      <c r="H163" s="1">
+        <v>2486</v>
+      </c>
+      <c r="I163" s="1">
+        <v>2207.33</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C164" s="1">
         <v>2461.2</v>
@@ -4005,10 +5481,19 @@
       <c r="F164" s="1">
         <v>1172.22</v>
       </c>
-    </row>
-    <row r="165" spans="1:6">
+      <c r="G164" s="1">
+        <v>948.7099999999999</v>
+      </c>
+      <c r="H164" s="1">
+        <v>1753.17</v>
+      </c>
+      <c r="I164" s="1">
+        <v>1909.84</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C165" s="1">
         <v>1423.28</v>
@@ -4022,10 +5507,19 @@
       <c r="F165" s="1">
         <v>2579.2</v>
       </c>
-    </row>
-    <row r="166" spans="1:6">
+      <c r="G165" s="1">
+        <v>1221.93</v>
+      </c>
+      <c r="H165" s="1">
+        <v>2663.26</v>
+      </c>
+      <c r="I165" s="1">
+        <v>3251.419999999999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C166" s="1">
         <v>1347.99</v>
@@ -4039,10 +5533,19 @@
       <c r="F166" s="1">
         <v>1286.36</v>
       </c>
-    </row>
-    <row r="167" spans="1:6">
+      <c r="G166" s="1">
+        <v>590.85</v>
+      </c>
+      <c r="H166" s="1">
+        <v>1501.64</v>
+      </c>
+      <c r="I166" s="1">
+        <v>800.14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C167" s="1">
         <v>4124.37</v>
@@ -4051,15 +5554,24 @@
         <v>8179.089999999998</v>
       </c>
       <c r="E167" s="1">
-        <v>5078.229999999999</v>
+        <v>5078.229999999998</v>
       </c>
       <c r="F167" s="1">
         <v>3454.02</v>
       </c>
-    </row>
-    <row r="168" spans="1:6">
+      <c r="G167" s="1">
+        <v>6761.789999999999</v>
+      </c>
+      <c r="H167" s="1">
+        <v>4428.789999999999</v>
+      </c>
+      <c r="I167" s="1">
+        <v>5314.91</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C168" s="1">
         <v>487.74</v>
@@ -4073,10 +5585,19 @@
       <c r="F168" s="1">
         <v>1183.08</v>
       </c>
-    </row>
-    <row r="169" spans="1:6">
+      <c r="G168" s="1">
+        <v>1558.26</v>
+      </c>
+      <c r="H168" s="1">
+        <v>2574.76</v>
+      </c>
+      <c r="I168" s="1">
+        <v>1499.05</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C169" s="1">
         <v>2584.44</v>
@@ -4085,15 +5606,24 @@
         <v>2938.44</v>
       </c>
       <c r="E169" s="1">
-        <v>2977.760000000001</v>
+        <v>2977.76</v>
       </c>
       <c r="F169" s="1">
-        <v>5470.070000000001</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
+        <v>5470.07</v>
+      </c>
+      <c r="G169" s="1">
+        <v>5642.02</v>
+      </c>
+      <c r="H169" s="1">
+        <v>3641.919999999999</v>
+      </c>
+      <c r="I169" s="1">
+        <v>2991.57</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C170" s="1">
         <v>911.74</v>
@@ -4107,10 +5637,19 @@
       <c r="F170" s="1">
         <v>550.46</v>
       </c>
-    </row>
-    <row r="171" spans="1:6">
+      <c r="G170" s="1">
+        <v>1071.82</v>
+      </c>
+      <c r="H170" s="1">
+        <v>1095.51</v>
+      </c>
+      <c r="I170" s="1">
+        <v>967.59</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C171" s="1">
         <v>2239.23</v>
@@ -4124,10 +5663,19 @@
       <c r="F171" s="1">
         <v>1621.45</v>
       </c>
-    </row>
-    <row r="172" spans="1:6">
+      <c r="G171" s="1">
+        <v>1513.13</v>
+      </c>
+      <c r="H171" s="1">
+        <v>2055.89</v>
+      </c>
+      <c r="I171" s="1">
+        <v>2728.239999999999</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C172" s="1">
         <v>2416.28</v>
@@ -4141,10 +5689,19 @@
       <c r="F172" s="1">
         <v>2080.11</v>
       </c>
-    </row>
-    <row r="173" spans="1:6">
+      <c r="G172" s="1">
+        <v>2946.400000000001</v>
+      </c>
+      <c r="H172" s="1">
+        <v>2807.869999999999</v>
+      </c>
+      <c r="I172" s="1">
+        <v>2536.39</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C173" s="1">
         <v>5237.139999999999</v>
@@ -4158,10 +5715,19 @@
       <c r="F173" s="1">
         <v>1955.33</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
+      <c r="G173" s="1">
+        <v>4192.74</v>
+      </c>
+      <c r="H173" s="1">
+        <v>3677.179999999999</v>
+      </c>
+      <c r="I173" s="1">
+        <v>3270.169999999999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C174" s="1">
         <v>1769.73</v>
@@ -4175,10 +5741,19 @@
       <c r="F174" s="1">
         <v>1846.39</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
+      <c r="G174" s="1">
+        <v>2279.62</v>
+      </c>
+      <c r="H174" s="1">
+        <v>2275.17</v>
+      </c>
+      <c r="I174" s="1">
+        <v>1672.9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C175" s="1">
         <v>2931.96</v>
@@ -4192,10 +5767,19 @@
       <c r="F175" s="1">
         <v>2849.76</v>
       </c>
-    </row>
-    <row r="176" spans="1:6">
+      <c r="G175" s="1">
+        <v>1271.73</v>
+      </c>
+      <c r="H175" s="1">
+        <v>400.76</v>
+      </c>
+      <c r="I175" s="1">
+        <v>1748.41</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C176" s="1">
         <v>1220.82</v>
@@ -4209,10 +5793,19 @@
       <c r="F176" s="1">
         <v>1126.24</v>
       </c>
-    </row>
-    <row r="177" spans="1:6">
+      <c r="G176" s="1">
+        <v>911.8000000000002</v>
+      </c>
+      <c r="H176" s="1">
+        <v>1674.24</v>
+      </c>
+      <c r="I176" s="1">
+        <v>1355.71</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C177" s="1">
         <v>1357.42</v>
@@ -4226,10 +5819,19 @@
       <c r="F177" s="1">
         <v>2306.92</v>
       </c>
-    </row>
-    <row r="178" spans="1:6">
+      <c r="G177" s="1">
+        <v>2142.23</v>
+      </c>
+      <c r="H177" s="1">
+        <v>2159.84</v>
+      </c>
+      <c r="I177" s="1">
+        <v>2109.82</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C178" s="1">
         <v>495.52</v>
@@ -4243,10 +5845,19 @@
       <c r="F178" s="1">
         <v>2509.04</v>
       </c>
-    </row>
-    <row r="179" spans="1:6">
+      <c r="G178" s="1">
+        <v>2911.49</v>
+      </c>
+      <c r="H178" s="1">
+        <v>742.48</v>
+      </c>
+      <c r="I178" s="1">
+        <v>982.1700000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C179" s="1">
         <v>134.98</v>
@@ -4260,16 +5871,25 @@
       <c r="F179" s="1">
         <v>854.75</v>
       </c>
-    </row>
-    <row r="180" spans="1:6">
+      <c r="G179" s="1">
+        <v>1183.08</v>
+      </c>
+      <c r="H179" s="1">
+        <v>562.96</v>
+      </c>
+      <c r="I179" s="1">
+        <v>484.6500000000001</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C180" s="1">
         <v>1698.92</v>
       </c>
       <c r="D180" s="1">
-        <v>908.8599999999999</v>
+        <v>908.8600000000001</v>
       </c>
       <c r="E180" s="1">
         <v>1034.22</v>
@@ -4277,10 +5897,19 @@
       <c r="F180" s="1">
         <v>1344.84</v>
       </c>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="G180" s="1">
+        <v>1062.72</v>
+      </c>
+      <c r="H180" s="1">
+        <v>2462.64</v>
+      </c>
+      <c r="I180" s="1">
+        <v>1400.79</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C181" s="1">
         <v>833.1799999999999</v>
@@ -4294,27 +5923,45 @@
       <c r="F181" s="1">
         <v>784.9</v>
       </c>
-    </row>
-    <row r="182" spans="1:6">
+      <c r="G181" s="1">
+        <v>903.72</v>
+      </c>
+      <c r="H181" s="1">
+        <v>742.37</v>
+      </c>
+      <c r="I181" s="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C182" s="1">
-        <v>857.39</v>
+        <v>857.3900000000001</v>
       </c>
       <c r="D182" s="1">
         <v>699.3299999999999</v>
       </c>
       <c r="E182" s="1">
-        <v>960.1899999999998</v>
+        <v>960.1900000000001</v>
       </c>
       <c r="F182" s="1">
         <v>428.8200000000001</v>
       </c>
-    </row>
-    <row r="183" spans="1:6">
+      <c r="G182" s="1">
+        <v>1949.76</v>
+      </c>
+      <c r="H182" s="1">
+        <v>926.2299999999999</v>
+      </c>
+      <c r="I182" s="1">
+        <v>712.6600000000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C183" s="1">
         <v>901.73</v>
@@ -4328,27 +5975,45 @@
       <c r="F183" s="1">
         <v>773.05</v>
       </c>
-    </row>
-    <row r="184" spans="1:6">
+      <c r="G183" s="1">
+        <v>1087.58</v>
+      </c>
+      <c r="H183" s="1">
+        <v>1446.45</v>
+      </c>
+      <c r="I183" s="1">
+        <v>1743.02</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C184" s="1">
         <v>1366.14</v>
       </c>
       <c r="D184" s="1">
-        <v>4865.34</v>
+        <v>4865.339999999999</v>
       </c>
       <c r="E184" s="1">
-        <v>3847.35</v>
+        <v>3847.349999999999</v>
       </c>
       <c r="F184" s="1">
         <v>3775.2</v>
       </c>
-    </row>
-    <row r="185" spans="1:6">
+      <c r="G184" s="1">
+        <v>1462.19</v>
+      </c>
+      <c r="H184" s="1">
+        <v>3300.14</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C185" s="1">
         <v>2629.69</v>
@@ -4360,12 +6025,21 @@
         <v>4249.28</v>
       </c>
       <c r="F185" s="1">
-        <v>6017.68</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
+        <v>6017.679999999998</v>
+      </c>
+      <c r="G185" s="1">
+        <v>2170.02</v>
+      </c>
+      <c r="H185" s="1">
+        <v>3737.339999999999</v>
+      </c>
+      <c r="I185" s="1">
+        <v>4079.570000000001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C186" s="1">
         <v>3160.669999999999</v>
@@ -4374,18 +6048,27 @@
         <v>3009.73</v>
       </c>
       <c r="E186" s="1">
-        <v>706.3</v>
+        <v>706.3000000000002</v>
       </c>
       <c r="F186" s="1">
         <v>2595.9</v>
       </c>
-    </row>
-    <row r="187" spans="1:6">
+      <c r="G186" s="1">
+        <v>2504.95</v>
+      </c>
+      <c r="H186" s="1">
+        <v>2045.57</v>
+      </c>
+      <c r="I186" s="1">
+        <v>1294.83</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C187" s="1">
-        <v>2331.449999999999</v>
+        <v>2331.45</v>
       </c>
       <c r="D187" s="1">
         <v>2223.42</v>
@@ -4396,44 +6079,71 @@
       <c r="F187" s="1">
         <v>2876.36</v>
       </c>
-    </row>
-    <row r="188" spans="1:6">
+      <c r="G187" s="1">
+        <v>2594.32</v>
+      </c>
+      <c r="H187" s="1">
+        <v>1590.32</v>
+      </c>
+      <c r="I187" s="1">
+        <v>853.8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C188" s="1">
-        <v>4397.359999999999</v>
+        <v>4397.360000000001</v>
       </c>
       <c r="D188" s="1">
         <v>4256.57</v>
       </c>
       <c r="E188" s="1">
-        <v>5204.46</v>
+        <v>5204.459999999999</v>
       </c>
       <c r="F188" s="1">
-        <v>4743.679999999999</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
+        <v>4743.68</v>
+      </c>
+      <c r="G188" s="1">
+        <v>6362.92</v>
+      </c>
+      <c r="H188" s="1">
+        <v>5252.139999999999</v>
+      </c>
+      <c r="I188" s="1">
+        <v>5661.329999999998</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C189" s="1">
         <v>3706.52</v>
       </c>
       <c r="D189" s="1">
-        <v>3073.969999999999</v>
+        <v>3073.97</v>
       </c>
       <c r="E189" s="1">
-        <v>2418.39</v>
+        <v>2418.389999999999</v>
       </c>
       <c r="F189" s="1">
         <v>2710.03</v>
       </c>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="G189" s="1">
+        <v>2647.32</v>
+      </c>
+      <c r="H189" s="1">
+        <v>2999.55</v>
+      </c>
+      <c r="I189" s="1">
+        <v>2984.399999999999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C190" s="1">
         <v>1314.17</v>
@@ -4447,16 +6157,25 @@
       <c r="F190" s="1">
         <v>2074.39</v>
       </c>
-    </row>
-    <row r="191" spans="1:6">
+      <c r="G190" s="1">
+        <v>395.94</v>
+      </c>
+      <c r="H190" s="1">
+        <v>1004.65</v>
+      </c>
+      <c r="I190" s="1">
+        <v>809.9299999999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C191" s="1">
         <v>1665.16</v>
       </c>
       <c r="D191" s="1">
-        <v>675.3900000000001</v>
+        <v>675.39</v>
       </c>
       <c r="E191" s="1">
         <v>1817.34</v>
@@ -4464,10 +6183,19 @@
       <c r="F191" s="1">
         <v>1275.21</v>
       </c>
-    </row>
-    <row r="192" spans="1:6">
+      <c r="G191" s="1">
+        <v>493.6300000000001</v>
+      </c>
+      <c r="H191" s="1">
+        <v>1488.99</v>
+      </c>
+      <c r="I191" s="1">
+        <v>207.17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C192" s="1">
         <v>1182.52</v>
@@ -4481,16 +6209,25 @@
       <c r="F192" s="1">
         <v>1355.48</v>
       </c>
-    </row>
-    <row r="193" spans="1:6">
+      <c r="G192" s="1">
+        <v>1277.57</v>
+      </c>
+      <c r="H192" s="1">
+        <v>1043.68</v>
+      </c>
+      <c r="I192" s="1">
+        <v>2112.07</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C193" s="1">
         <v>294.02</v>
       </c>
       <c r="D193" s="1">
-        <v>924.21</v>
+        <v>924.2099999999999</v>
       </c>
       <c r="E193" s="1">
         <v>2474.14</v>
@@ -4498,16 +6235,25 @@
       <c r="F193" s="1">
         <v>2889.39</v>
       </c>
-    </row>
-    <row r="194" spans="1:6">
+      <c r="G193" s="1">
+        <v>1150.18</v>
+      </c>
+      <c r="H193" s="1">
+        <v>3307.689999999999</v>
+      </c>
+      <c r="I193" s="1">
+        <v>1760.81</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C194" s="1">
         <v>5639.7</v>
       </c>
       <c r="D194" s="1">
-        <v>3828.32</v>
+        <v>3828.319999999999</v>
       </c>
       <c r="E194" s="1">
         <v>2548.03</v>
@@ -4515,13 +6261,22 @@
       <c r="F194" s="1">
         <v>5499.349999999999</v>
       </c>
-    </row>
-    <row r="195" spans="1:6">
+      <c r="G194" s="1">
+        <v>3055.079999999999</v>
+      </c>
+      <c r="H194" s="1">
+        <v>4879.03</v>
+      </c>
+      <c r="I194" s="1">
+        <v>2032.14</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C195" s="1">
-        <v>2975.060000000001</v>
+        <v>2975.06</v>
       </c>
       <c r="D195" s="1">
         <v>1955.62</v>
@@ -4532,16 +6287,25 @@
       <c r="F195" s="1">
         <v>1260.05</v>
       </c>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="G195" s="1">
+        <v>1814.02</v>
+      </c>
+      <c r="H195" s="1">
+        <v>3495.879999999998</v>
+      </c>
+      <c r="I195" s="1">
+        <v>1924.71</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C196" s="1">
         <v>708.5</v>
       </c>
       <c r="D196" s="1">
-        <v>614.3499999999999</v>
+        <v>614.35</v>
       </c>
       <c r="E196" s="1">
         <v>714.5599999999999</v>
@@ -4549,16 +6313,25 @@
       <c r="F196" s="1">
         <v>500.25</v>
       </c>
-    </row>
-    <row r="197" spans="1:6">
+      <c r="G196" s="1">
+        <v>1696.09</v>
+      </c>
+      <c r="H196" s="1">
+        <v>2101.95</v>
+      </c>
+      <c r="I196" s="1">
+        <v>1789.3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C197" s="1">
         <v>2869.92</v>
       </c>
       <c r="D197" s="1">
-        <v>2489.529999999999</v>
+        <v>2489.53</v>
       </c>
       <c r="E197" s="1">
         <v>3807.73</v>
@@ -4566,10 +6339,19 @@
       <c r="F197" s="1">
         <v>2128.09</v>
       </c>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="G197" s="1">
+        <v>1609.69</v>
+      </c>
+      <c r="H197" s="1">
+        <v>2788.46</v>
+      </c>
+      <c r="I197" s="1">
+        <v>3083.649999999999</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C198" s="1">
         <v>1810.62</v>
@@ -4583,10 +6365,19 @@
       <c r="F198" s="1">
         <v>2452.58</v>
       </c>
-    </row>
-    <row r="199" spans="1:6">
+      <c r="G198" s="1">
+        <v>3968.809999999999</v>
+      </c>
+      <c r="H198" s="1">
+        <v>2087.45</v>
+      </c>
+      <c r="I198" s="1">
+        <v>3247.46</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C199" s="1">
         <v>975.42</v>
@@ -4595,38 +6386,56 @@
         <v>881.21</v>
       </c>
       <c r="E199" s="1">
-        <v>534.3100000000001</v>
+        <v>534.3099999999999</v>
       </c>
       <c r="F199" s="1">
         <v>84.47</v>
       </c>
-    </row>
-    <row r="200" spans="1:6">
+      <c r="G199" s="1">
+        <v>817.8000000000002</v>
+      </c>
+      <c r="H199" s="1">
+        <v>781.97</v>
+      </c>
+      <c r="I199" s="1">
+        <v>1136.81</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C200" s="1">
-        <v>2415</v>
+        <v>2414.999999999999</v>
       </c>
       <c r="D200" s="1">
         <v>1012.32</v>
       </c>
       <c r="E200" s="1">
-        <v>435.2</v>
+        <v>435.1999999999999</v>
       </c>
       <c r="F200" s="1">
-        <v>643.3700000000001</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
+        <v>643.37</v>
+      </c>
+      <c r="G200" s="1">
+        <v>565.1899999999999</v>
+      </c>
+      <c r="H200" s="1">
+        <v>1599.56</v>
+      </c>
+      <c r="I200" s="1">
+        <v>1850.16</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C201" s="1">
-        <v>3693.47</v>
+        <v>3693.469999999999</v>
       </c>
       <c r="D201" s="1">
-        <v>4067.12</v>
+        <v>4067.119999999999</v>
       </c>
       <c r="E201" s="1">
         <v>4220.32</v>
@@ -4634,10 +6443,19 @@
       <c r="F201" s="1">
         <v>5367.85</v>
       </c>
-    </row>
-    <row r="202" spans="1:6">
+      <c r="G201" s="1">
+        <v>3554.91</v>
+      </c>
+      <c r="H201" s="1">
+        <v>6418.699999999999</v>
+      </c>
+      <c r="I201" s="1">
+        <v>4664.42</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C202" s="1">
         <v>1848.83</v>
@@ -4651,16 +6469,25 @@
       <c r="F202" s="1">
         <v>587.29</v>
       </c>
-    </row>
-    <row r="203" spans="1:6">
+      <c r="G202" s="1">
+        <v>1551.89</v>
+      </c>
+      <c r="H202" s="1">
+        <v>1500.83</v>
+      </c>
+      <c r="I202" s="1">
+        <v>1755.3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C203" s="1">
         <v>235.76</v>
       </c>
       <c r="D203" s="1">
-        <v>437.31</v>
+        <v>437.3100000000001</v>
       </c>
       <c r="E203" s="1">
         <v>212.8</v>
@@ -4668,10 +6495,19 @@
       <c r="F203" s="1">
         <v>733.71</v>
       </c>
-    </row>
-    <row r="204" spans="1:6">
+      <c r="G203" s="1">
+        <v>251.99</v>
+      </c>
+      <c r="H203" s="1">
+        <v>968.9400000000001</v>
+      </c>
+      <c r="I203" s="1">
+        <v>1924.47</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C204" s="1">
         <v>14.69</v>
@@ -4685,10 +6521,19 @@
       <c r="F204" s="1">
         <v>968.71</v>
       </c>
-    </row>
-    <row r="205" spans="1:6">
+      <c r="G204" s="1">
+        <v>587.25</v>
+      </c>
+      <c r="H204" s="1">
+        <v>536.97</v>
+      </c>
+      <c r="I204" s="1">
+        <v>927.9200000000001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C205" s="1">
         <v>694.74</v>
@@ -4702,10 +6547,19 @@
       <c r="F205" s="1">
         <v>2124.33</v>
       </c>
-    </row>
-    <row r="206" spans="1:6">
+      <c r="G205" s="1">
+        <v>748.0400000000001</v>
+      </c>
+      <c r="H205" s="1">
+        <v>1428.69</v>
+      </c>
+      <c r="I205" s="1">
+        <v>394.46</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C206" s="1">
         <v>1569.24</v>
@@ -4719,10 +6573,19 @@
       <c r="F206" s="1">
         <v>1571.75</v>
       </c>
-    </row>
-    <row r="207" spans="1:6">
+      <c r="G206" s="1">
+        <v>465.17</v>
+      </c>
+      <c r="H206" s="1">
+        <v>589.15</v>
+      </c>
+      <c r="I206" s="1">
+        <v>1658.26</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C207" s="1">
         <v>2026.43</v>
@@ -4736,10 +6599,19 @@
       <c r="F207" s="1">
         <v>853.6600000000001</v>
       </c>
-    </row>
-    <row r="208" spans="1:6">
+      <c r="G207" s="1">
+        <v>1823.42</v>
+      </c>
+      <c r="H207" s="1">
+        <v>1312.64</v>
+      </c>
+      <c r="I207" s="1">
+        <v>1233.74</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C208" s="1">
         <v>914.9400000000001</v>
@@ -4753,10 +6625,19 @@
       <c r="F208" s="1">
         <v>1289.16</v>
       </c>
-    </row>
-    <row r="209" spans="1:6">
+      <c r="G208" s="1">
+        <v>929.7900000000001</v>
+      </c>
+      <c r="H208" s="1">
+        <v>728.03</v>
+      </c>
+      <c r="I208" s="1">
+        <v>858.0599999999999</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C209" s="1">
         <v>275.12</v>
@@ -4770,10 +6651,19 @@
       <c r="F209" s="1">
         <v>244.68</v>
       </c>
-    </row>
-    <row r="210" spans="1:6">
+      <c r="G209" s="1">
+        <v>552.3</v>
+      </c>
+      <c r="H209" s="1">
+        <v>1862.92</v>
+      </c>
+      <c r="I209" s="1">
+        <v>610.9299999999999</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C210" s="1">
         <v>492.45</v>
@@ -4782,15 +6672,24 @@
         <v>502.02</v>
       </c>
       <c r="E210" s="1">
-        <v>836.54</v>
+        <v>836.5400000000001</v>
       </c>
       <c r="F210" s="1">
         <v>1140.16</v>
       </c>
-    </row>
-    <row r="211" spans="1:6">
+      <c r="G210" s="1">
+        <v>1464.57</v>
+      </c>
+      <c r="H210" s="1">
+        <v>909.1100000000001</v>
+      </c>
+      <c r="I210" s="1">
+        <v>1443.52</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C211" s="1">
         <v>1015.12</v>
@@ -4804,13 +6703,22 @@
       <c r="F211" s="1">
         <v>424.46</v>
       </c>
-    </row>
-    <row r="212" spans="1:6">
+      <c r="G211" s="1">
+        <v>1169.78</v>
+      </c>
+      <c r="H211" s="1">
+        <v>1373.5</v>
+      </c>
+      <c r="I211" s="1">
+        <v>1943.08</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C212" s="1">
-        <v>2716.559999999999</v>
+        <v>2716.56</v>
       </c>
       <c r="D212" s="1">
         <v>2311.85</v>
@@ -4821,10 +6729,19 @@
       <c r="F212" s="1">
         <v>2262.73</v>
       </c>
-    </row>
-    <row r="213" spans="1:6">
+      <c r="G212" s="1">
+        <v>2532.07</v>
+      </c>
+      <c r="H212" s="1">
+        <v>3157.96</v>
+      </c>
+      <c r="I212" s="1">
+        <v>2299.14</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C213" s="1">
         <v>507.77</v>
@@ -4838,13 +6755,22 @@
       <c r="F213" s="1">
         <v>356.17</v>
       </c>
-    </row>
-    <row r="214" spans="1:6">
+      <c r="G213" s="1">
+        <v>1053.46</v>
+      </c>
+      <c r="H213" s="1">
+        <v>2008.12</v>
+      </c>
+      <c r="I213" s="1">
+        <v>1278.64</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D214" s="1">
         <v>1938.12</v>
@@ -4853,12 +6779,21 @@
         <v>230.87</v>
       </c>
       <c r="F214" s="1">
-        <v>515.95</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
+        <v>515.9499999999999</v>
+      </c>
+      <c r="G214" s="1">
+        <v>865.1400000000001</v>
+      </c>
+      <c r="H214" s="1">
+        <v>1044.24</v>
+      </c>
+      <c r="I214" s="1">
+        <v>363.77</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C215" s="1">
         <v>2341.6</v>
@@ -4872,10 +6807,19 @@
       <c r="F215" s="1">
         <v>2093.44</v>
       </c>
-    </row>
-    <row r="216" spans="1:6">
+      <c r="G215" s="1">
+        <v>2319.33</v>
+      </c>
+      <c r="H215" s="1">
+        <v>2539.63</v>
+      </c>
+      <c r="I215" s="1">
+        <v>1955.82</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C216" s="1">
         <v>722.51</v>
@@ -4889,10 +6833,19 @@
       <c r="F216" s="1">
         <v>503.5700000000001</v>
       </c>
-    </row>
-    <row r="217" spans="1:6">
+      <c r="G216" s="1">
+        <v>1302.59</v>
+      </c>
+      <c r="H216" s="1">
+        <v>1131.49</v>
+      </c>
+      <c r="I216" s="1">
+        <v>1254.07</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C217" s="1">
         <v>1038.28</v>
@@ -4906,10 +6859,19 @@
       <c r="F217" s="1">
         <v>370.41</v>
       </c>
-    </row>
-    <row r="218" spans="1:6">
+      <c r="G217" s="1">
+        <v>1090.43</v>
+      </c>
+      <c r="H217" s="1">
+        <v>1177.08</v>
+      </c>
+      <c r="I217" s="1">
+        <v>84.98999999999999</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C218" s="1">
         <v>1183.07</v>
@@ -4923,16 +6885,25 @@
       <c r="F218" s="1">
         <v>1281.34</v>
       </c>
-    </row>
-    <row r="219" spans="1:6">
+      <c r="G218" s="1">
+        <v>1457.72</v>
+      </c>
+      <c r="H218" s="1">
+        <v>696.9400000000001</v>
+      </c>
+      <c r="I218" s="1">
+        <v>1092.95</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C219" s="1">
         <v>839.5700000000001</v>
       </c>
       <c r="D219" s="1">
-        <v>945.1100000000001</v>
+        <v>945.11</v>
       </c>
       <c r="E219" s="1">
         <v>1353.77</v>
@@ -4940,10 +6911,19 @@
       <c r="F219" s="1">
         <v>999.8</v>
       </c>
-    </row>
-    <row r="220" spans="1:6">
+      <c r="G219" s="1">
+        <v>1533.61</v>
+      </c>
+      <c r="H219" s="1">
+        <v>1337.01</v>
+      </c>
+      <c r="I219" s="1">
+        <v>1026.81</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C220" s="1">
         <v>543.9</v>
@@ -4957,13 +6937,22 @@
       <c r="F220" s="1">
         <v>608.8099999999999</v>
       </c>
-    </row>
-    <row r="221" spans="1:6">
+      <c r="G220" s="1">
+        <v>181.97</v>
+      </c>
+      <c r="H220" s="1">
+        <v>594.26</v>
+      </c>
+      <c r="I220" s="1">
+        <v>379.95</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C221" s="1">
-        <v>669.88</v>
+        <v>669.8799999999999</v>
       </c>
       <c r="D221" s="1">
         <v>360.25</v>
@@ -4974,13 +6963,22 @@
       <c r="F221" s="1">
         <v>95.98999999999999</v>
       </c>
-    </row>
-    <row r="222" spans="1:6">
+      <c r="G221" s="1">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="H221" s="1">
+        <v>263.95</v>
+      </c>
+      <c r="I221" s="1">
+        <v>128.07</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C222" s="1">
-        <v>2604.779999999999</v>
+        <v>2604.78</v>
       </c>
       <c r="D222" s="1">
         <v>2934.72</v>
@@ -4991,10 +6989,19 @@
       <c r="F222" s="1">
         <v>2900.599999999999</v>
       </c>
-    </row>
-    <row r="223" spans="1:6">
+      <c r="G222" s="1">
+        <v>1547.51</v>
+      </c>
+      <c r="H222" s="1">
+        <v>2545.890000000001</v>
+      </c>
+      <c r="I222" s="1">
+        <v>3862.459999999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C223" s="1">
         <v>1384.49</v>
@@ -5008,10 +7015,19 @@
       <c r="F223" s="1">
         <v>1715.92</v>
       </c>
-    </row>
-    <row r="224" spans="1:6">
+      <c r="G223" s="1">
+        <v>949.5700000000001</v>
+      </c>
+      <c r="H223" s="1">
+        <v>1114.5</v>
+      </c>
+      <c r="I223" s="1">
+        <v>949.0200000000001</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C224" s="1">
         <v>3707.669999999999</v>
@@ -5025,10 +7041,19 @@
       <c r="F224" s="1">
         <v>3544.48</v>
       </c>
-    </row>
-    <row r="225" spans="1:6">
+      <c r="G224" s="1">
+        <v>2164.43</v>
+      </c>
+      <c r="H224" s="1">
+        <v>5322.55</v>
+      </c>
+      <c r="I224" s="1">
+        <v>1813.31</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C225" s="1">
         <v>472.59</v>
@@ -5042,10 +7067,19 @@
       <c r="F225" s="1">
         <v>503.96</v>
       </c>
-    </row>
-    <row r="226" spans="1:6">
+      <c r="G225" s="1">
+        <v>353.97</v>
+      </c>
+      <c r="H225" s="1">
+        <v>773.21</v>
+      </c>
+      <c r="I225" s="1">
+        <v>726.91</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C226" s="1">
         <v>1828.45</v>
@@ -5059,16 +7093,25 @@
       <c r="F226" s="1">
         <v>1155.98</v>
       </c>
-    </row>
-    <row r="227" spans="1:6">
+      <c r="G226" s="1">
+        <v>1503.86</v>
+      </c>
+      <c r="H226" s="1">
+        <v>1199.47</v>
+      </c>
+      <c r="I226" s="1">
+        <v>3377.91</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C227" s="1">
         <v>1630.22</v>
       </c>
       <c r="D227" s="1">
-        <v>3193.59</v>
+        <v>3193.589999999999</v>
       </c>
       <c r="E227" s="1">
         <v>3052.67</v>
@@ -5076,10 +7119,19 @@
       <c r="F227" s="1">
         <v>2280.81</v>
       </c>
-    </row>
-    <row r="228" spans="1:6">
+      <c r="G227" s="1">
+        <v>2036.36</v>
+      </c>
+      <c r="H227" s="1">
+        <v>1677.08</v>
+      </c>
+      <c r="I227" s="1">
+        <v>2559.14</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C228" s="1">
         <v>1420.8</v>
@@ -5093,10 +7145,19 @@
       <c r="F228" s="1">
         <v>1298.28</v>
       </c>
-    </row>
-    <row r="229" spans="1:6">
+      <c r="G228" s="1">
+        <v>3079.73</v>
+      </c>
+      <c r="H228" s="1">
+        <v>3964.38</v>
+      </c>
+      <c r="I228" s="1">
+        <v>1597.94</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C229" s="1">
         <v>375.96</v>
@@ -5110,10 +7171,19 @@
       <c r="F229" s="1">
         <v>1813.97</v>
       </c>
-    </row>
-    <row r="230" spans="1:6">
+      <c r="G229" s="1">
+        <v>1163.26</v>
+      </c>
+      <c r="H229" s="1">
+        <v>1623.67</v>
+      </c>
+      <c r="I229" s="1">
+        <v>1320.62</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C230" s="1">
         <v>1668.89</v>
@@ -5127,16 +7197,25 @@
       <c r="F230" s="1">
         <v>1386.98</v>
       </c>
-    </row>
-    <row r="231" spans="1:6">
+      <c r="G230" s="1">
+        <v>1957.38</v>
+      </c>
+      <c r="H230" s="1">
+        <v>1830.57</v>
+      </c>
+      <c r="I230" s="1">
+        <v>2061.54</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C231" s="1">
         <v>1520.24</v>
       </c>
       <c r="D231" s="1">
-        <v>474.16</v>
+        <v>474.1599999999999</v>
       </c>
       <c r="E231" s="1">
         <v>377.05</v>
@@ -5144,10 +7223,19 @@
       <c r="F231" s="1">
         <v>1456.96</v>
       </c>
-    </row>
-    <row r="232" spans="1:6">
+      <c r="G231" s="1">
+        <v>2155.57</v>
+      </c>
+      <c r="H231" s="1">
+        <v>2518.599999999999</v>
+      </c>
+      <c r="I231" s="1">
+        <v>1134.14</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C232" s="1">
         <v>2110.19</v>
@@ -5159,12 +7247,21 @@
         <v>1577.28</v>
       </c>
       <c r="F232" s="1">
-        <v>931.1799999999998</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
+        <v>931.1799999999999</v>
+      </c>
+      <c r="G232" s="1">
+        <v>1736.2</v>
+      </c>
+      <c r="H232" s="1">
+        <v>2702.65</v>
+      </c>
+      <c r="I232" s="1">
+        <v>2071.92</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C233" s="1">
         <v>1835.31</v>
@@ -5178,10 +7275,19 @@
       <c r="F233" s="1">
         <v>2371.8</v>
       </c>
-    </row>
-    <row r="234" spans="1:6">
+      <c r="G233" s="1">
+        <v>1898.55</v>
+      </c>
+      <c r="H233" s="1">
+        <v>2427.88</v>
+      </c>
+      <c r="I233" s="1">
+        <v>3410.310000000001</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C234" s="1">
         <v>3755.16</v>
@@ -5193,12 +7299,21 @@
         <v>2920.369999999999</v>
       </c>
       <c r="F234" s="1">
-        <v>2248.56</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
+        <v>2507.49</v>
+      </c>
+      <c r="G234" s="1">
+        <v>2831.64</v>
+      </c>
+      <c r="H234" s="1">
+        <v>2580.649999999999</v>
+      </c>
+      <c r="I234" s="1">
+        <v>2521.509999999999</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C235" s="1">
         <v>1908.9</v>
@@ -5207,15 +7322,24 @@
         <v>2101.18</v>
       </c>
       <c r="E235" s="1">
-        <v>4211.179999999998</v>
+        <v>4211.18</v>
       </c>
       <c r="F235" s="1">
         <v>1678.83</v>
       </c>
-    </row>
-    <row r="236" spans="1:6">
+      <c r="G235" s="1">
+        <v>2294.66</v>
+      </c>
+      <c r="H235" s="1">
+        <v>1869.44</v>
+      </c>
+      <c r="I235" s="1">
+        <v>1121.31</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C236" s="1">
         <v>1703.32</v>
@@ -5229,10 +7353,19 @@
       <c r="F236" s="1">
         <v>1266.13</v>
       </c>
-    </row>
-    <row r="237" spans="1:6">
+      <c r="G236" s="1">
+        <v>2632.389999999999</v>
+      </c>
+      <c r="H236" s="1">
+        <v>2640.799999999999</v>
+      </c>
+      <c r="I236" s="1">
+        <v>1949.12</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C237" s="1">
         <v>2858.27</v>
@@ -5246,10 +7379,19 @@
       <c r="F237" s="1">
         <v>1245.23</v>
       </c>
-    </row>
-    <row r="238" spans="1:6">
+      <c r="G237" s="1">
+        <v>2865.969999999998</v>
+      </c>
+      <c r="H237" s="1">
+        <v>3946.53</v>
+      </c>
+      <c r="I237" s="1">
+        <v>1585.82</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C238" s="1">
         <v>1021.56</v>
@@ -5263,10 +7405,19 @@
       <c r="F238" s="1">
         <v>973.54</v>
       </c>
-    </row>
-    <row r="239" spans="1:6">
+      <c r="G238" s="1">
+        <v>2265.16</v>
+      </c>
+      <c r="H238" s="1">
+        <v>579.71</v>
+      </c>
+      <c r="I238" s="1">
+        <v>542.4200000000001</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C239" s="1">
         <v>1406.38</v>
@@ -5278,12 +7429,21 @@
         <v>1644.84</v>
       </c>
       <c r="F239" s="1">
-        <v>771.36</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6">
+        <v>771.3599999999999</v>
+      </c>
+      <c r="G239" s="1">
+        <v>1427.78</v>
+      </c>
+      <c r="H239" s="1">
+        <v>539.6899999999999</v>
+      </c>
+      <c r="I239" s="1">
+        <v>1112.07</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C240" s="1">
         <v>1022.48</v>
@@ -5297,10 +7457,19 @@
       <c r="F240" s="1">
         <v>2061.22</v>
       </c>
-    </row>
-    <row r="241" spans="1:6">
+      <c r="G240" s="1">
+        <v>1906.84</v>
+      </c>
+      <c r="H240" s="1">
+        <v>2218.83</v>
+      </c>
+      <c r="I240" s="1">
+        <v>2335.39</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C241" s="1">
         <v>503.96</v>
@@ -5314,10 +7483,19 @@
       <c r="F241" s="1">
         <v>137.68</v>
       </c>
-    </row>
-    <row r="242" spans="1:6">
+      <c r="G241" s="1">
+        <v>537.21</v>
+      </c>
+      <c r="H241" s="1">
+        <v>1674.7</v>
+      </c>
+      <c r="I241" s="1">
+        <v>929.7900000000001</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C242" s="1">
         <v>4401.52</v>
@@ -5329,15 +7507,24 @@
         <v>2387.7</v>
       </c>
       <c r="F242" s="1">
-        <v>3617.96</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
+        <v>3617.959999999999</v>
+      </c>
+      <c r="G242" s="1">
+        <v>3217</v>
+      </c>
+      <c r="H242" s="1">
+        <v>4495.009999999998</v>
+      </c>
+      <c r="I242" s="1">
+        <v>2798.66</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C243" s="1">
-        <v>3261.869999999999</v>
+        <v>3261.87</v>
       </c>
       <c r="D243" s="1">
         <v>1938.83</v>
@@ -5348,10 +7535,19 @@
       <c r="F243" s="1">
         <v>1633.82</v>
       </c>
-    </row>
-    <row r="244" spans="1:6">
+      <c r="G243" s="1">
+        <v>1491.32</v>
+      </c>
+      <c r="H243" s="1">
+        <v>2570.6</v>
+      </c>
+      <c r="I243" s="1">
+        <v>2548.66</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C244" s="1">
         <v>1104.2</v>
@@ -5365,10 +7561,19 @@
       <c r="F244" s="1">
         <v>378.96</v>
       </c>
-    </row>
-    <row r="245" spans="1:6">
+      <c r="G244" s="1">
+        <v>1640.73</v>
+      </c>
+      <c r="H244" s="1">
+        <v>2321.37</v>
+      </c>
+      <c r="I244" s="1">
+        <v>2164.14</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C245" s="1">
         <v>1662.84</v>
@@ -5382,13 +7587,22 @@
       <c r="F245" s="1">
         <v>1865.74</v>
       </c>
-    </row>
-    <row r="246" spans="1:6">
+      <c r="G245" s="1">
+        <v>3001.18</v>
+      </c>
+      <c r="H245" s="1">
+        <v>3088.74</v>
+      </c>
+      <c r="I245" s="1">
+        <v>5441.559999999998</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C246" s="1">
-        <v>2801.889999999999</v>
+        <v>2801.89</v>
       </c>
       <c r="D246" s="1">
         <v>2412.35</v>
@@ -5397,12 +7611,21 @@
         <v>2027.14</v>
       </c>
       <c r="F246" s="1">
-        <v>3094.92</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
+        <v>3094.919999999999</v>
+      </c>
+      <c r="G246" s="1">
+        <v>4559.819999999999</v>
+      </c>
+      <c r="H246" s="1">
+        <v>3739.259999999999</v>
+      </c>
+      <c r="I246" s="1">
+        <v>1757.52</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C247" s="1">
         <v>1403.03</v>
@@ -5416,27 +7639,45 @@
       <c r="F247" s="1">
         <v>2413.24</v>
       </c>
-    </row>
-    <row r="248" spans="1:6">
+      <c r="G247" s="1">
+        <v>1679.47</v>
+      </c>
+      <c r="H247" s="1">
+        <v>2197.72</v>
+      </c>
+      <c r="I247" s="1">
+        <v>2595.99</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C248" s="1">
         <v>4297.77</v>
       </c>
       <c r="D248" s="1">
-        <v>4279.54</v>
+        <v>4279.539999999998</v>
       </c>
       <c r="E248" s="1">
         <v>3528.52</v>
       </c>
       <c r="F248" s="1">
-        <v>3800.81</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
+        <v>3800.809999999999</v>
+      </c>
+      <c r="G248" s="1">
+        <v>4244.860000000001</v>
+      </c>
+      <c r="H248" s="1">
+        <v>5605.699999999998</v>
+      </c>
+      <c r="I248" s="1">
+        <v>4160.529999999999</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C249" s="1">
         <v>1459.76</v>
@@ -5450,10 +7691,19 @@
       <c r="F249" s="1">
         <v>1788.44</v>
       </c>
-    </row>
-    <row r="250" spans="1:6">
+      <c r="G249" s="1">
+        <v>2923.389999999999</v>
+      </c>
+      <c r="H249" s="1">
+        <v>2222.42</v>
+      </c>
+      <c r="I249" s="1">
+        <v>441.89</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C250" s="1">
         <v>6233.06</v>
@@ -5462,15 +7712,24 @@
         <v>9348.769999999999</v>
       </c>
       <c r="E250" s="1">
-        <v>7277.29</v>
+        <v>7277.289999999999</v>
       </c>
       <c r="F250" s="1">
         <v>9756.1</v>
       </c>
-    </row>
-    <row r="251" spans="1:6">
+      <c r="G250" s="1">
+        <v>5765.999999999999</v>
+      </c>
+      <c r="H250" s="1">
+        <v>6833.68</v>
+      </c>
+      <c r="I250" s="1">
+        <v>7152.839999999998</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C251" s="1">
         <v>1324.23</v>
@@ -5484,10 +7743,19 @@
       <c r="F251" s="1">
         <v>688.4000000000001</v>
       </c>
-    </row>
-    <row r="252" spans="1:6">
+      <c r="G251" s="1">
+        <v>2015.71</v>
+      </c>
+      <c r="H251" s="1">
+        <v>2241.6</v>
+      </c>
+      <c r="I251" s="1">
+        <v>1847.77</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C252" s="1">
         <v>698.98</v>
@@ -5501,13 +7769,22 @@
       <c r="F252" s="1">
         <v>339.97</v>
       </c>
-    </row>
-    <row r="253" spans="1:6">
+      <c r="G252" s="1">
+        <v>856.62</v>
+      </c>
+      <c r="H252" s="1">
+        <v>1645.62</v>
+      </c>
+      <c r="I252" s="1">
+        <v>902.73</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C253" s="1">
-        <v>2907.11</v>
+        <v>2907.109999999999</v>
       </c>
       <c r="D253" s="1">
         <v>2050.9</v>
@@ -5518,16 +7795,25 @@
       <c r="F253" s="1">
         <v>1645.71</v>
       </c>
-    </row>
-    <row r="254" spans="1:6">
+      <c r="G253" s="1">
+        <v>2081.77</v>
+      </c>
+      <c r="H253" s="1">
+        <v>2546.79</v>
+      </c>
+      <c r="I253" s="1">
+        <v>2498.69</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C254" s="1">
         <v>1670.24</v>
       </c>
       <c r="D254" s="1">
-        <v>522.0100000000001</v>
+        <v>522.01</v>
       </c>
       <c r="E254" s="1">
         <v>1086.34</v>
@@ -5535,27 +7821,45 @@
       <c r="F254" s="1">
         <v>586.3099999999999</v>
       </c>
-    </row>
-    <row r="255" spans="1:6">
+      <c r="G254" s="1">
+        <v>167.98</v>
+      </c>
+      <c r="H254" s="1">
+        <v>821.8099999999999</v>
+      </c>
+      <c r="I254" s="1">
+        <v>1639.86</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C255" s="1">
         <v>3457.51</v>
       </c>
       <c r="D255" s="1">
-        <v>5504.43</v>
+        <v>5504.429999999998</v>
       </c>
       <c r="E255" s="1">
-        <v>4283.73</v>
+        <v>4283.729999999999</v>
       </c>
       <c r="F255" s="1">
         <v>2101.51</v>
       </c>
-    </row>
-    <row r="256" spans="1:6">
+      <c r="G255" s="1">
+        <v>2921.449999999999</v>
+      </c>
+      <c r="H255" s="1">
+        <v>3951.55</v>
+      </c>
+      <c r="I255" s="1">
+        <v>3066.21</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C256" s="1">
         <v>805.01</v>
@@ -5569,10 +7873,19 @@
       <c r="F256" s="1">
         <v>915.97</v>
       </c>
-    </row>
-    <row r="257" spans="1:6">
+      <c r="G256" s="1">
+        <v>652.25</v>
+      </c>
+      <c r="H256" s="1">
+        <v>205.98</v>
+      </c>
+      <c r="I256" s="1">
+        <v>245.58</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C257" s="1">
         <v>2366.01</v>
@@ -5586,13 +7899,22 @@
       <c r="F257" s="1">
         <v>3576.96</v>
       </c>
-    </row>
-    <row r="258" spans="1:6">
+      <c r="G257" s="1">
+        <v>1183.3</v>
+      </c>
+      <c r="H257" s="1">
+        <v>2936.9</v>
+      </c>
+      <c r="I257" s="1">
+        <v>2337.8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C258" s="1">
-        <v>784.22</v>
+        <v>784.2199999999999</v>
       </c>
       <c r="D258" s="1">
         <v>1621.32</v>
@@ -5603,10 +7925,19 @@
       <c r="F258" s="1">
         <v>2173.43</v>
       </c>
-    </row>
-    <row r="259" spans="1:6">
+      <c r="G258" s="1">
+        <v>1549.91</v>
+      </c>
+      <c r="H258" s="1">
+        <v>1350.31</v>
+      </c>
+      <c r="I258" s="1">
+        <v>1834.47</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C259" s="1">
         <v>2486.75</v>
@@ -5620,10 +7951,19 @@
       <c r="F259" s="1">
         <v>1590.81</v>
       </c>
-    </row>
-    <row r="260" spans="1:6">
+      <c r="G259" s="1">
+        <v>1516.11</v>
+      </c>
+      <c r="H259" s="1">
+        <v>3018.449999999999</v>
+      </c>
+      <c r="I259" s="1">
+        <v>1635.29</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C260" s="1">
         <v>2171.6</v>
@@ -5637,10 +7977,19 @@
       <c r="F260" s="1">
         <v>3734.6</v>
       </c>
-    </row>
-    <row r="261" spans="1:6">
+      <c r="G260" s="1">
+        <v>2940.619999999999</v>
+      </c>
+      <c r="H260" s="1">
+        <v>4152.300000000001</v>
+      </c>
+      <c r="I260" s="1">
+        <v>3208.77</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C261" s="1">
         <v>1722.07</v>
@@ -5654,16 +8003,25 @@
       <c r="F261" s="1">
         <v>1533.94</v>
       </c>
-    </row>
-    <row r="262" spans="1:6">
+      <c r="G261" s="1">
+        <v>1566.11</v>
+      </c>
+      <c r="H261" s="1">
+        <v>2087.57</v>
+      </c>
+      <c r="I261" s="1">
+        <v>989.2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C262" s="1">
         <v>5427.579999999999</v>
       </c>
       <c r="D262" s="1">
-        <v>3151.62</v>
+        <v>3151.619999999999</v>
       </c>
       <c r="E262" s="1">
         <v>4239.2</v>
@@ -5671,16 +8029,25 @@
       <c r="F262" s="1">
         <v>2607.34</v>
       </c>
-    </row>
-    <row r="263" spans="1:6">
+      <c r="G262" s="1">
+        <v>4115.46</v>
+      </c>
+      <c r="H262" s="1">
+        <v>4039.96</v>
+      </c>
+      <c r="I262" s="1">
+        <v>2725.36</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C263" s="1">
         <v>1849.19</v>
       </c>
       <c r="D263" s="1">
-        <v>1646.17</v>
+        <v>1956.15</v>
       </c>
       <c r="E263" s="1">
         <v>2410.51</v>
@@ -5688,16 +8055,25 @@
       <c r="F263" s="1">
         <v>2391.6</v>
       </c>
-    </row>
-    <row r="264" spans="1:6">
+      <c r="G263" s="1">
+        <v>1873.47</v>
+      </c>
+      <c r="H263" s="1">
+        <v>2555.97</v>
+      </c>
+      <c r="I263" s="1">
+        <v>3079.98</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C264" s="1">
         <v>2359.86</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E264" s="1">
         <v>682.2099999999999</v>
@@ -5705,10 +8081,19 @@
       <c r="F264" s="1">
         <v>763.88</v>
       </c>
-    </row>
-    <row r="265" spans="1:6">
+      <c r="G264" s="1">
+        <v>1226.9</v>
+      </c>
+      <c r="H264" s="1">
+        <v>930.8</v>
+      </c>
+      <c r="I264" s="1">
+        <v>1657.54</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C265" s="1">
         <v>4485.74</v>
@@ -5717,15 +8102,24 @@
         <v>4510.21</v>
       </c>
       <c r="E265" s="1">
-        <v>5236.359999999999</v>
+        <v>5236.36</v>
       </c>
       <c r="F265" s="1">
         <v>4730.419999999999</v>
       </c>
-    </row>
-    <row r="266" spans="1:6">
+      <c r="G265" s="1">
+        <v>3310.18</v>
+      </c>
+      <c r="H265" s="1">
+        <v>3381.52</v>
+      </c>
+      <c r="I265" s="1">
+        <v>5966.369999999999</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C266" s="1">
         <v>2547.01</v>
@@ -5737,12 +8131,21 @@
         <v>3245.389999999999</v>
       </c>
       <c r="F266" s="1">
-        <v>2770.529999999999</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+        <v>2770.53</v>
+      </c>
+      <c r="G266" s="1">
+        <v>1075.25</v>
+      </c>
+      <c r="H266" s="1">
+        <v>3915.08</v>
+      </c>
+      <c r="I266" s="1">
+        <v>2498.35</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C267" s="1">
         <v>2724.05</v>
@@ -5756,10 +8159,19 @@
       <c r="F267" s="1">
         <v>1494.74</v>
       </c>
-    </row>
-    <row r="268" spans="1:6">
+      <c r="G267" s="1">
+        <v>1730.19</v>
+      </c>
+      <c r="H267" s="1">
+        <v>3988.49</v>
+      </c>
+      <c r="I267" s="1">
+        <v>1744.92</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C268" s="1">
         <v>1618.48</v>
@@ -5768,21 +8180,30 @@
         <v>1592.84</v>
       </c>
       <c r="E268" s="1">
-        <v>689.61</v>
+        <v>689.6100000000001</v>
       </c>
       <c r="F268" s="1">
         <v>1189.7</v>
       </c>
-    </row>
-    <row r="269" spans="1:6">
+      <c r="G268" s="1">
+        <v>1031.83</v>
+      </c>
+      <c r="H268" s="1">
+        <v>1267.43</v>
+      </c>
+      <c r="I268" s="1">
+        <v>920.4100000000001</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C269" s="1">
         <v>801.25</v>
       </c>
       <c r="D269" s="1">
-        <v>782.3</v>
+        <v>782.3000000000002</v>
       </c>
       <c r="E269" s="1">
         <v>1382.38</v>
@@ -5790,22 +8211,40 @@
       <c r="F269" s="1">
         <v>221.21</v>
       </c>
-    </row>
-    <row r="270" spans="1:6">
+      <c r="G269" s="1">
+        <v>511.71</v>
+      </c>
+      <c r="H269" s="1">
+        <v>1258.11</v>
+      </c>
+      <c r="I269" s="1">
+        <v>454.84</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C270" s="1">
         <v>472.9000000000001</v>
       </c>
       <c r="D270" s="1">
-        <v>535.2</v>
+        <v>535.1999999999999</v>
       </c>
       <c r="E270" s="1">
         <v>807.0599999999999</v>
       </c>
       <c r="F270" s="1">
         <v>696.0700000000001</v>
+      </c>
+      <c r="G270" s="1">
+        <v>873.76</v>
+      </c>
+      <c r="H270" s="1">
+        <v>192.23</v>
+      </c>
+      <c r="I270" s="1">
+        <v>552.9400000000001</v>
       </c>
     </row>
   </sheetData>
